--- a/research/traditional_assets/database/data/belgium/belgium_steel.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_steel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09615818772040137</v>
+        <v>0.09595154225110036</v>
       </c>
       <c r="C2">
-        <v>2547.341892575248</v>
+        <v>2527.885996846429</v>
       </c>
       <c r="D2">
-        <v>2032.341892575247</v>
+        <v>2040.715996846429</v>
       </c>
       <c r="E2">
-        <v>-965.2</v>
+        <v>-937.37</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27.83</v>
       </c>
       <c r="G2">
         <v>515</v>
@@ -1451,28 +1451,28 @@
         <v>394.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.399849</v>
       </c>
       <c r="N2">
-        <v>394.4</v>
+        <v>393.000151</v>
       </c>
       <c r="O2">
-        <v>98.59999999999999</v>
+        <v>98.25003774999999</v>
       </c>
       <c r="P2">
-        <v>295.8</v>
+        <v>294.75011325</v>
       </c>
       <c r="Q2">
-        <v>448.9</v>
+        <v>447.85011325</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09615818772040137</v>
+        <v>0.09653968914252563</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161359</v>
+        <v>0.9890109831215612</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>281.7446738898266</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09595154225110036</v>
+        <v>0.09574489678179939</v>
       </c>
       <c r="C3">
-        <v>2527.885996846429</v>
+        <v>2508.49939631366</v>
       </c>
       <c r="D3">
-        <v>2040.715996846429</v>
+        <v>2049.15939631366</v>
       </c>
       <c r="E3">
-        <v>-937.37</v>
+        <v>-909.5400000000001</v>
       </c>
       <c r="F3">
-        <v>27.83</v>
+        <v>55.66</v>
       </c>
       <c r="G3">
         <v>515</v>
@@ -1533,28 +1533,28 @@
         <v>394.4</v>
       </c>
       <c r="M3">
-        <v>1.399849</v>
+        <v>2.799698</v>
       </c>
       <c r="N3">
-        <v>393.000151</v>
+        <v>391.600302</v>
       </c>
       <c r="O3">
-        <v>98.25003774999999</v>
+        <v>97.9000755</v>
       </c>
       <c r="P3">
-        <v>294.75011325</v>
+        <v>293.7002265</v>
       </c>
       <c r="Q3">
-        <v>447.85011325</v>
+        <v>446.8002265</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09653968914252563</v>
+        <v>0.09692897630795855</v>
       </c>
       <c r="T3">
-        <v>0.9890109831215612</v>
+        <v>0.9965989145556686</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>281.7446738898266</v>
+        <v>140.8723369449133</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09574489678179939</v>
+        <v>0.09553825131249837</v>
       </c>
       <c r="C4">
-        <v>2508.49939631366</v>
+        <v>2489.182954670655</v>
       </c>
       <c r="D4">
-        <v>2049.15939631366</v>
+        <v>2057.672954670655</v>
       </c>
       <c r="E4">
-        <v>-909.5400000000001</v>
+        <v>-881.71</v>
       </c>
       <c r="F4">
-        <v>55.66</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="G4">
         <v>515</v>
@@ -1615,28 +1615,28 @@
         <v>394.4</v>
       </c>
       <c r="M4">
-        <v>2.799698</v>
+        <v>4.199547</v>
       </c>
       <c r="N4">
-        <v>391.600302</v>
+        <v>390.200453</v>
       </c>
       <c r="O4">
-        <v>97.9000755</v>
+        <v>97.55011325</v>
       </c>
       <c r="P4">
-        <v>293.7002265</v>
+        <v>292.65033975</v>
       </c>
       <c r="Q4">
-        <v>446.8002265</v>
+        <v>445.75033975</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09692897630795855</v>
+        <v>0.09732629001288491</v>
       </c>
       <c r="T4">
-        <v>0.9965989145556686</v>
+        <v>1.004343298184294</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>140.8723369449133</v>
+        <v>93.9148912966089</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09553825131249837</v>
+        <v>0.09533160584319736</v>
       </c>
       <c r="C5">
-        <v>2489.182954670655</v>
+        <v>2469.937550024417</v>
       </c>
       <c r="D5">
-        <v>2057.672954670655</v>
+        <v>2066.257550024417</v>
       </c>
       <c r="E5">
-        <v>-881.71</v>
+        <v>-853.88</v>
       </c>
       <c r="F5">
-        <v>83.48999999999999</v>
+        <v>111.32</v>
       </c>
       <c r="G5">
         <v>515</v>
@@ -1697,28 +1697,28 @@
         <v>394.4</v>
       </c>
       <c r="M5">
-        <v>4.199547</v>
+        <v>5.599396</v>
       </c>
       <c r="N5">
-        <v>390.200453</v>
+        <v>388.800604</v>
       </c>
       <c r="O5">
-        <v>97.55011325</v>
+        <v>97.20015099999999</v>
       </c>
       <c r="P5">
-        <v>292.65033975</v>
+        <v>291.600453</v>
       </c>
       <c r="Q5">
-        <v>445.75033975</v>
+        <v>444.700453</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09732629001288491</v>
+        <v>0.09773188108666392</v>
       </c>
       <c r="T5">
-        <v>1.004343298184294</v>
+        <v>1.012249023138515</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>93.9148912966089</v>
+        <v>70.43616847245666</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09533160584319736</v>
+        <v>0.09512496037389637</v>
       </c>
       <c r="C6">
-        <v>2469.937550024417</v>
+        <v>2450.764075197167</v>
       </c>
       <c r="D6">
-        <v>2066.257550024417</v>
+        <v>2074.914075197167</v>
       </c>
       <c r="E6">
-        <v>-853.88</v>
+        <v>-826.0500000000001</v>
       </c>
       <c r="F6">
-        <v>111.32</v>
+        <v>139.15</v>
       </c>
       <c r="G6">
         <v>515</v>
@@ -1779,28 +1779,28 @@
         <v>394.4</v>
       </c>
       <c r="M6">
-        <v>5.599396</v>
+        <v>6.999245</v>
       </c>
       <c r="N6">
-        <v>388.800604</v>
+        <v>387.400755</v>
       </c>
       <c r="O6">
-        <v>97.20015099999999</v>
+        <v>96.85018875</v>
       </c>
       <c r="P6">
-        <v>291.600453</v>
+        <v>290.55056625</v>
       </c>
       <c r="Q6">
-        <v>444.700453</v>
+        <v>443.65056625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09773188108666392</v>
+        <v>0.09814601091989091</v>
       </c>
       <c r="T6">
-        <v>1.012249023138515</v>
+        <v>1.020321184407562</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>70.43616847245666</v>
+        <v>56.34893477796534</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09512496037389637</v>
+        <v>0.09491831490459536</v>
       </c>
       <c r="C7">
-        <v>2450.764075197167</v>
+        <v>2431.66343803588</v>
       </c>
       <c r="D7">
-        <v>2074.914075197167</v>
+        <v>2083.64343803588</v>
       </c>
       <c r="E7">
-        <v>-826.0500000000001</v>
+        <v>-798.22</v>
       </c>
       <c r="F7">
-        <v>139.15</v>
+        <v>166.98</v>
       </c>
       <c r="G7">
         <v>515</v>
@@ -1861,28 +1861,28 @@
         <v>394.4</v>
       </c>
       <c r="M7">
-        <v>6.999245</v>
+        <v>8.399094</v>
       </c>
       <c r="N7">
-        <v>387.400755</v>
+        <v>386.000906</v>
       </c>
       <c r="O7">
-        <v>96.85018875</v>
+        <v>96.5002265</v>
       </c>
       <c r="P7">
-        <v>290.55056625</v>
+        <v>289.5006795</v>
       </c>
       <c r="Q7">
-        <v>443.65056625</v>
+        <v>442.6006795</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09814601091989091</v>
+        <v>0.09856895202616528</v>
       </c>
       <c r="T7">
-        <v>1.020321184407562</v>
+        <v>1.028565093788717</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>56.34893477796534</v>
+        <v>46.95744564830445</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09491831490459536</v>
+        <v>0.09471166943529434</v>
       </c>
       <c r="C8">
-        <v>2431.66343803588</v>
+        <v>2412.636561729676</v>
       </c>
       <c r="D8">
-        <v>2083.64343803588</v>
+        <v>2092.446561729676</v>
       </c>
       <c r="E8">
-        <v>-798.22</v>
+        <v>-770.3900000000001</v>
       </c>
       <c r="F8">
-        <v>166.98</v>
+        <v>194.81</v>
       </c>
       <c r="G8">
         <v>515</v>
@@ -1943,28 +1943,28 @@
         <v>394.4</v>
       </c>
       <c r="M8">
-        <v>8.399094</v>
+        <v>9.798942999999998</v>
       </c>
       <c r="N8">
-        <v>386.000906</v>
+        <v>384.601057</v>
       </c>
       <c r="O8">
-        <v>96.5002265</v>
+        <v>96.15026424999999</v>
       </c>
       <c r="P8">
-        <v>289.5006795</v>
+        <v>288.45079275</v>
       </c>
       <c r="Q8">
-        <v>442.6006795</v>
+        <v>441.55079275</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09856895202616528</v>
+        <v>0.09900098864010144</v>
       </c>
       <c r="T8">
-        <v>1.028565093788717</v>
+        <v>1.03698629154366</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.95744564830445</v>
+        <v>40.2492391271181</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09471166943529433</v>
+        <v>0.09450502396599336</v>
       </c>
       <c r="C9">
-        <v>2412.636561729676</v>
+        <v>2393.684385135281</v>
       </c>
       <c r="D9">
-        <v>2092.446561729676</v>
+        <v>2101.32438513528</v>
       </c>
       <c r="E9">
-        <v>-770.39</v>
+        <v>-742.5600000000001</v>
       </c>
       <c r="F9">
-        <v>194.81</v>
+        <v>222.64</v>
       </c>
       <c r="G9">
         <v>515</v>
@@ -2025,28 +2025,28 @@
         <v>394.4</v>
       </c>
       <c r="M9">
-        <v>9.798943000000001</v>
+        <v>11.198792</v>
       </c>
       <c r="N9">
-        <v>384.601057</v>
+        <v>383.201208</v>
       </c>
       <c r="O9">
-        <v>96.15026424999999</v>
+        <v>95.80030199999999</v>
       </c>
       <c r="P9">
-        <v>288.45079275</v>
+        <v>287.400906</v>
       </c>
       <c r="Q9">
-        <v>441.55079275</v>
+        <v>440.500906</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09900098864010144</v>
+        <v>0.0994424173543406</v>
       </c>
       <c r="T9">
-        <v>1.03698629154366</v>
+        <v>1.045590558815015</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.24923912711809</v>
+        <v>35.21808423622833</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09450502396599336</v>
+        <v>0.09429837849669234</v>
       </c>
       <c r="C10">
-        <v>2393.684385135281</v>
+        <v>2374.807863110829</v>
       </c>
       <c r="D10">
-        <v>2101.32438513528</v>
+        <v>2110.277863110829</v>
       </c>
       <c r="E10">
-        <v>-742.5600000000001</v>
+        <v>-714.73</v>
       </c>
       <c r="F10">
-        <v>222.64</v>
+        <v>250.47</v>
       </c>
       <c r="G10">
         <v>515</v>
@@ -2107,28 +2107,28 @@
         <v>394.4</v>
       </c>
       <c r="M10">
-        <v>11.198792</v>
+        <v>12.598641</v>
       </c>
       <c r="N10">
-        <v>383.201208</v>
+        <v>381.801359</v>
       </c>
       <c r="O10">
-        <v>95.80030199999999</v>
+        <v>95.45033975</v>
       </c>
       <c r="P10">
-        <v>287.400906</v>
+        <v>286.35101925</v>
       </c>
       <c r="Q10">
-        <v>440.500906</v>
+        <v>439.45101925</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0994424173543406</v>
+        <v>0.09989354779856301</v>
       </c>
       <c r="T10">
-        <v>1.045590558815015</v>
+        <v>1.054383930861563</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.21808423622833</v>
+        <v>31.3049637655363</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09429837849669234</v>
+        <v>0.09409173302739134</v>
       </c>
       <c r="C11">
-        <v>2374.807863110829</v>
+        <v>2356.007966858208</v>
       </c>
       <c r="D11">
-        <v>2110.277863110829</v>
+        <v>2119.307966858208</v>
       </c>
       <c r="E11">
-        <v>-714.73</v>
+        <v>-686.9000000000001</v>
       </c>
       <c r="F11">
-        <v>250.47</v>
+        <v>278.3</v>
       </c>
       <c r="G11">
         <v>515</v>
@@ -2189,28 +2189,28 @@
         <v>394.4</v>
       </c>
       <c r="M11">
-        <v>12.598641</v>
+        <v>13.99849</v>
       </c>
       <c r="N11">
-        <v>381.801359</v>
+        <v>380.40151</v>
       </c>
       <c r="O11">
-        <v>95.45033975</v>
+        <v>95.10037749999999</v>
       </c>
       <c r="P11">
-        <v>286.35101925</v>
+        <v>285.3011325</v>
       </c>
       <c r="Q11">
-        <v>439.45101925</v>
+        <v>438.4011325</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09989354779856301</v>
+        <v>0.1003547033637681</v>
       </c>
       <c r="T11">
-        <v>1.054383930861563</v>
+        <v>1.063372711175814</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.3049637655363</v>
+        <v>28.17446738898267</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09409173302739134</v>
+        <v>0.09388508755809034</v>
       </c>
       <c r="C12">
-        <v>2356.007966858208</v>
+        <v>2337.28568427425</v>
       </c>
       <c r="D12">
-        <v>2119.307966858208</v>
+        <v>2128.41568427425</v>
       </c>
       <c r="E12">
-        <v>-686.9000000000001</v>
+        <v>-659.0700000000001</v>
       </c>
       <c r="F12">
-        <v>278.3</v>
+        <v>306.13</v>
       </c>
       <c r="G12">
         <v>515</v>
@@ -2271,28 +2271,28 @@
         <v>394.4</v>
       </c>
       <c r="M12">
-        <v>13.99849</v>
+        <v>15.398339</v>
       </c>
       <c r="N12">
-        <v>380.40151</v>
+        <v>379.001661</v>
       </c>
       <c r="O12">
-        <v>95.10037749999999</v>
+        <v>94.75041524999999</v>
       </c>
       <c r="P12">
-        <v>285.3011325</v>
+        <v>284.25124575</v>
       </c>
       <c r="Q12">
-        <v>438.4011325</v>
+        <v>437.35124575</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1003547033637681</v>
+        <v>0.1008262219753824</v>
       </c>
       <c r="T12">
-        <v>1.063372711175814</v>
+        <v>1.072563486553306</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.17446738898267</v>
+        <v>25.61315217180243</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09388508755809034</v>
+        <v>0.09367844208878932</v>
       </c>
       <c r="C13">
-        <v>2337.28568427425</v>
+        <v>2318.642020311017</v>
       </c>
       <c r="D13">
-        <v>2128.41568427425</v>
+        <v>2137.602020311017</v>
       </c>
       <c r="E13">
-        <v>-659.0700000000001</v>
+        <v>-631.24</v>
       </c>
       <c r="F13">
-        <v>306.13</v>
+        <v>333.96</v>
       </c>
       <c r="G13">
         <v>515</v>
@@ -2353,28 +2353,28 @@
         <v>394.4</v>
       </c>
       <c r="M13">
-        <v>15.398339</v>
+        <v>16.798188</v>
       </c>
       <c r="N13">
-        <v>379.001661</v>
+        <v>377.601812</v>
       </c>
       <c r="O13">
-        <v>94.75041524999999</v>
+        <v>94.400453</v>
       </c>
       <c r="P13">
-        <v>284.25124575</v>
+        <v>283.201359</v>
       </c>
       <c r="Q13">
-        <v>437.35124575</v>
+        <v>436.301359</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1008262219753824</v>
+        <v>0.1013084569190788</v>
       </c>
       <c r="T13">
-        <v>1.072563486553306</v>
+        <v>1.081963143189377</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.61315217180243</v>
+        <v>23.47872282415223</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09367844208878932</v>
+        <v>0.09347179661948832</v>
       </c>
       <c r="C14">
-        <v>2318.642020311017</v>
+        <v>2300.077997345442</v>
       </c>
       <c r="D14">
-        <v>2137.602020311017</v>
+        <v>2146.867997345442</v>
       </c>
       <c r="E14">
-        <v>-631.24</v>
+        <v>-603.4100000000001</v>
       </c>
       <c r="F14">
-        <v>333.96</v>
+        <v>361.79</v>
       </c>
       <c r="G14">
         <v>515</v>
@@ -2435,28 +2435,28 @@
         <v>394.4</v>
       </c>
       <c r="M14">
-        <v>16.798188</v>
+        <v>18.198037</v>
       </c>
       <c r="N14">
-        <v>377.601812</v>
+        <v>376.201963</v>
       </c>
       <c r="O14">
-        <v>94.400453</v>
+        <v>94.05049074999999</v>
       </c>
       <c r="P14">
-        <v>283.201359</v>
+        <v>282.15147225</v>
       </c>
       <c r="Q14">
-        <v>436.301359</v>
+        <v>435.25147225</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1013084569190788</v>
+        <v>0.1018017777235498</v>
       </c>
       <c r="T14">
-        <v>1.081963143189377</v>
+        <v>1.091578883886048</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.47872282415223</v>
+        <v>21.67266722229436</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09347179661948832</v>
+        <v>0.09326515115018733</v>
       </c>
       <c r="C15">
-        <v>2300.077997345442</v>
+        <v>2281.594655558643</v>
       </c>
       <c r="D15">
-        <v>2146.867997345442</v>
+        <v>2156.214655558643</v>
       </c>
       <c r="E15">
-        <v>-603.4100000000001</v>
+        <v>-575.5799999999999</v>
       </c>
       <c r="F15">
-        <v>361.79</v>
+        <v>389.6200000000001</v>
       </c>
       <c r="G15">
         <v>515</v>
@@ -2517,28 +2517,28 @@
         <v>394.4</v>
       </c>
       <c r="M15">
-        <v>18.198037</v>
+        <v>19.597886</v>
       </c>
       <c r="N15">
-        <v>376.201963</v>
+        <v>374.802114</v>
       </c>
       <c r="O15">
-        <v>94.05049074999999</v>
+        <v>93.70052849999999</v>
       </c>
       <c r="P15">
-        <v>282.15147225</v>
+        <v>281.1015854999999</v>
       </c>
       <c r="Q15">
-        <v>435.25147225</v>
+        <v>434.2015855</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1018017777235498</v>
+        <v>0.102306571104869</v>
       </c>
       <c r="T15">
-        <v>1.091578883886048</v>
+        <v>1.101418246459385</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.67266722229436</v>
+        <v>20.12461956355904</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09326515115018733</v>
+        <v>0.09305850568088633</v>
       </c>
       <c r="C16">
-        <v>2281.594655558643</v>
+        <v>2263.193053325181</v>
       </c>
       <c r="D16">
-        <v>2156.214655558643</v>
+        <v>2165.643053325181</v>
       </c>
       <c r="E16">
-        <v>-575.5799999999999</v>
+        <v>-547.75</v>
       </c>
       <c r="F16">
-        <v>389.6200000000001</v>
+        <v>417.45</v>
       </c>
       <c r="G16">
         <v>515</v>
@@ -2599,28 +2599,28 @@
         <v>394.4</v>
       </c>
       <c r="M16">
-        <v>19.597886</v>
+        <v>20.997735</v>
       </c>
       <c r="N16">
-        <v>374.802114</v>
+        <v>373.402265</v>
       </c>
       <c r="O16">
-        <v>93.70052849999999</v>
+        <v>93.35056625</v>
       </c>
       <c r="P16">
-        <v>281.1015854999999</v>
+        <v>280.05169875</v>
       </c>
       <c r="Q16">
-        <v>434.2015855</v>
+        <v>433.15169875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.102306571104869</v>
+        <v>0.1028232419775133</v>
       </c>
       <c r="T16">
-        <v>1.101418246459385</v>
+        <v>1.111489123446213</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.12461956355904</v>
+        <v>18.78297825932178</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09305850568088633</v>
+        <v>0.09285186021158531</v>
       </c>
       <c r="C17">
-        <v>2263.193053325181</v>
+        <v>2244.874267612574</v>
       </c>
       <c r="D17">
-        <v>2165.643053325181</v>
+        <v>2175.154267612575</v>
       </c>
       <c r="E17">
-        <v>-547.75</v>
+        <v>-519.9200000000001</v>
       </c>
       <c r="F17">
-        <v>417.45</v>
+        <v>445.28</v>
       </c>
       <c r="G17">
         <v>515</v>
@@ -2681,28 +2681,28 @@
         <v>394.4</v>
       </c>
       <c r="M17">
-        <v>20.997735</v>
+        <v>22.397584</v>
       </c>
       <c r="N17">
-        <v>373.402265</v>
+        <v>372.002416</v>
       </c>
       <c r="O17">
-        <v>93.35056625</v>
+        <v>93.000604</v>
       </c>
       <c r="P17">
-        <v>280.05169875</v>
+        <v>279.001812</v>
       </c>
       <c r="Q17">
-        <v>433.15169875</v>
+        <v>432.101812</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1028232419775133</v>
+        <v>0.1033522145376016</v>
       </c>
       <c r="T17">
-        <v>1.111489123446213</v>
+        <v>1.121799783218441</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.78297825932178</v>
+        <v>17.60904211811416</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09285186021158531</v>
+        <v>0.09264521474228432</v>
       </c>
       <c r="C18">
-        <v>2244.874267612574</v>
+        <v>2226.639394391386</v>
       </c>
       <c r="D18">
-        <v>2175.154267612575</v>
+        <v>2184.749394391386</v>
       </c>
       <c r="E18">
-        <v>-519.9200000000001</v>
+        <v>-492.09</v>
       </c>
       <c r="F18">
-        <v>445.28</v>
+        <v>473.11</v>
       </c>
       <c r="G18">
         <v>515</v>
@@ -2763,28 +2763,28 @@
         <v>394.4</v>
       </c>
       <c r="M18">
-        <v>22.397584</v>
+        <v>23.797433</v>
       </c>
       <c r="N18">
-        <v>372.002416</v>
+        <v>370.602567</v>
       </c>
       <c r="O18">
-        <v>93.000604</v>
+        <v>92.65064174999999</v>
       </c>
       <c r="P18">
-        <v>279.001812</v>
+        <v>277.95192525</v>
       </c>
       <c r="Q18">
-        <v>432.101812</v>
+        <v>431.05192525</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1033522145376016</v>
+        <v>0.103893933424439</v>
       </c>
       <c r="T18">
-        <v>1.121799783218441</v>
+        <v>1.132358892623735</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.60904211811416</v>
+        <v>16.57321611116627</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09264521474228432</v>
+        <v>0.09243856927298331</v>
       </c>
       <c r="C19">
-        <v>2226.639394391386</v>
+        <v>2208.489549056221</v>
       </c>
       <c r="D19">
-        <v>2184.749394391386</v>
+        <v>2194.429549056221</v>
       </c>
       <c r="E19">
-        <v>-492.09</v>
+        <v>-464.26</v>
       </c>
       <c r="F19">
-        <v>473.11</v>
+        <v>500.9400000000001</v>
       </c>
       <c r="G19">
         <v>515</v>
@@ -2845,28 +2845,28 @@
         <v>394.4</v>
       </c>
       <c r="M19">
-        <v>23.797433</v>
+        <v>25.197282</v>
       </c>
       <c r="N19">
-        <v>370.602567</v>
+        <v>369.202718</v>
       </c>
       <c r="O19">
-        <v>92.65064174999999</v>
+        <v>92.3006795</v>
       </c>
       <c r="P19">
-        <v>277.95192525</v>
+        <v>276.9020385</v>
       </c>
       <c r="Q19">
-        <v>431.05192525</v>
+        <v>430.0020385</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.103893933424439</v>
+        <v>0.1044488649670528</v>
       </c>
       <c r="T19">
-        <v>1.132358892623735</v>
+        <v>1.143175541282817</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.57321611116627</v>
+        <v>15.65248188276815</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09243856927298333</v>
+        <v>0.09223192380368231</v>
       </c>
       <c r="C20">
-        <v>2208.48954905622</v>
+        <v>2190.425866857956</v>
       </c>
       <c r="D20">
-        <v>2194.42954905622</v>
+        <v>2204.195866857956</v>
       </c>
       <c r="E20">
-        <v>-464.26</v>
+        <v>-436.4300000000001</v>
       </c>
       <c r="F20">
-        <v>500.94</v>
+        <v>528.77</v>
       </c>
       <c r="G20">
         <v>515</v>
@@ -2927,28 +2927,28 @@
         <v>394.4</v>
       </c>
       <c r="M20">
-        <v>25.197282</v>
+        <v>26.597131</v>
       </c>
       <c r="N20">
-        <v>369.202718</v>
+        <v>367.802869</v>
       </c>
       <c r="O20">
-        <v>92.3006795</v>
+        <v>91.95071725</v>
       </c>
       <c r="P20">
-        <v>276.9020385</v>
+        <v>275.85215175</v>
       </c>
       <c r="Q20">
-        <v>430.0020385</v>
+        <v>428.95215175</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1044488649670528</v>
+        <v>0.1050174985230646</v>
       </c>
       <c r="T20">
-        <v>1.143175541282817</v>
+        <v>1.154259267686567</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.65248188276815</v>
+        <v>14.82866704683298</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09223192380368231</v>
+        <v>0.0920252783343813</v>
       </c>
       <c r="C21">
-        <v>2190.425866857956</v>
+        <v>2172.44950334757</v>
       </c>
       <c r="D21">
-        <v>2204.195866857956</v>
+        <v>2214.049503347569</v>
       </c>
       <c r="E21">
-        <v>-436.4300000000001</v>
+        <v>-408.6</v>
       </c>
       <c r="F21">
-        <v>528.77</v>
+        <v>556.6</v>
       </c>
       <c r="G21">
         <v>515</v>
@@ -3009,28 +3009,28 @@
         <v>394.4</v>
       </c>
       <c r="M21">
-        <v>26.597131</v>
+        <v>27.99698</v>
       </c>
       <c r="N21">
-        <v>367.802869</v>
+        <v>366.40302</v>
       </c>
       <c r="O21">
-        <v>91.95071725</v>
+        <v>91.60075499999999</v>
       </c>
       <c r="P21">
-        <v>275.85215175</v>
+        <v>274.802265</v>
       </c>
       <c r="Q21">
-        <v>428.95215175</v>
+        <v>427.902265</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1050174985230646</v>
+        <v>0.1056003479179766</v>
       </c>
       <c r="T21">
-        <v>1.154259267686567</v>
+        <v>1.165620087250411</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.82866704683298</v>
+        <v>14.08723369449133</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0920252783343813</v>
+        <v>0.09181863286508031</v>
       </c>
       <c r="C22">
-        <v>2172.44950334757</v>
+        <v>2154.561634831924</v>
       </c>
       <c r="D22">
-        <v>2214.049503347569</v>
+        <v>2223.991634831925</v>
       </c>
       <c r="E22">
-        <v>-408.6</v>
+        <v>-380.77</v>
       </c>
       <c r="F22">
-        <v>556.6</v>
+        <v>584.4300000000001</v>
       </c>
       <c r="G22">
         <v>515</v>
@@ -3091,28 +3091,28 @@
         <v>394.4</v>
       </c>
       <c r="M22">
-        <v>27.99698</v>
+        <v>29.396829</v>
       </c>
       <c r="N22">
-        <v>366.40302</v>
+        <v>365.003171</v>
       </c>
       <c r="O22">
-        <v>91.60075499999999</v>
+        <v>91.25079274999999</v>
       </c>
       <c r="P22">
-        <v>274.802265</v>
+        <v>273.75237825</v>
       </c>
       <c r="Q22">
-        <v>427.902265</v>
+        <v>426.85237825</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1056003479179766</v>
+        <v>0.1061979529937725</v>
       </c>
       <c r="T22">
-        <v>1.165620087250411</v>
+        <v>1.177268522499416</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.08723369449133</v>
+        <v>13.4164130423727</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0918186328650803</v>
+        <v>0.0918594873957793</v>
       </c>
       <c r="C23">
-        <v>2154.561634831925</v>
+        <v>2124.758965580554</v>
       </c>
       <c r="D23">
-        <v>2223.991634831925</v>
+        <v>2222.018965580554</v>
       </c>
       <c r="E23">
-        <v>-380.7700000000001</v>
+        <v>-352.9400000000001</v>
       </c>
       <c r="F23">
-        <v>584.4299999999999</v>
+        <v>612.26</v>
       </c>
       <c r="G23">
         <v>515</v>
@@ -3173,45 +3173,45 @@
         <v>394.4</v>
       </c>
       <c r="M23">
-        <v>29.396829</v>
+        <v>31.715068</v>
       </c>
       <c r="N23">
-        <v>365.003171</v>
+        <v>362.684932</v>
       </c>
       <c r="O23">
-        <v>91.25079274999999</v>
+        <v>90.671233</v>
       </c>
       <c r="P23">
-        <v>273.75237825</v>
+        <v>272.013699</v>
       </c>
       <c r="Q23">
-        <v>426.85237825</v>
+        <v>425.113699</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1061979529937725</v>
+        <v>0.1068108812766401</v>
       </c>
       <c r="T23">
-        <v>1.177268522499416</v>
+        <v>1.189215635575319</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.4164130423727</v>
+        <v>12.43572928804693</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0918594873957793</v>
+        <v>0.0916640919264783</v>
       </c>
       <c r="C24">
-        <v>2124.758965580554</v>
+        <v>2106.395465849901</v>
       </c>
       <c r="D24">
-        <v>2222.018965580554</v>
+        <v>2231.485465849901</v>
       </c>
       <c r="E24">
-        <v>-352.9400000000001</v>
+        <v>-325.11</v>
       </c>
       <c r="F24">
-        <v>612.26</v>
+        <v>640.09</v>
       </c>
       <c r="G24">
         <v>515</v>
@@ -3255,28 +3255,28 @@
         <v>394.4</v>
       </c>
       <c r="M24">
-        <v>31.715068</v>
+        <v>33.156662</v>
       </c>
       <c r="N24">
-        <v>362.684932</v>
+        <v>361.243338</v>
       </c>
       <c r="O24">
-        <v>90.671233</v>
+        <v>90.3108345</v>
       </c>
       <c r="P24">
-        <v>272.013699</v>
+        <v>270.9325035</v>
       </c>
       <c r="Q24">
-        <v>425.113699</v>
+        <v>424.0325035</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1068108812766401</v>
+        <v>0.1074397297746471</v>
       </c>
       <c r="T24">
-        <v>1.189215635575319</v>
+        <v>1.201473063276569</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.43572928804693</v>
+        <v>11.89504540595793</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0916640919264783</v>
+        <v>0.0914686964571773</v>
       </c>
       <c r="C25">
-        <v>2106.395465849901</v>
+        <v>2088.112971771095</v>
       </c>
       <c r="D25">
-        <v>2231.485465849901</v>
+        <v>2241.032971771095</v>
       </c>
       <c r="E25">
-        <v>-325.11</v>
+        <v>-297.28</v>
       </c>
       <c r="F25">
-        <v>640.09</v>
+        <v>667.9200000000001</v>
       </c>
       <c r="G25">
         <v>515</v>
@@ -3337,28 +3337,28 @@
         <v>394.4</v>
       </c>
       <c r="M25">
-        <v>33.156662</v>
+        <v>34.59825600000001</v>
       </c>
       <c r="N25">
-        <v>361.243338</v>
+        <v>359.801744</v>
       </c>
       <c r="O25">
-        <v>90.3108345</v>
+        <v>89.950436</v>
       </c>
       <c r="P25">
-        <v>270.9325035</v>
+        <v>269.851308</v>
       </c>
       <c r="Q25">
-        <v>424.0325035</v>
+        <v>422.951308</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1074397297746471</v>
+        <v>0.1080851269173385</v>
       </c>
       <c r="T25">
-        <v>1.201473063276569</v>
+        <v>1.214053054864694</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.89504540595793</v>
+        <v>11.39941851404302</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0914686964571773</v>
+        <v>0.0912733009878763</v>
       </c>
       <c r="C26">
-        <v>2088.112971771095</v>
+        <v>2069.912527570331</v>
       </c>
       <c r="D26">
-        <v>2241.032971771095</v>
+        <v>2250.662527570331</v>
       </c>
       <c r="E26">
-        <v>-297.2800000000001</v>
+        <v>-269.45</v>
       </c>
       <c r="F26">
-        <v>667.92</v>
+        <v>695.75</v>
       </c>
       <c r="G26">
         <v>515</v>
@@ -3419,28 +3419,28 @@
         <v>394.4</v>
       </c>
       <c r="M26">
-        <v>34.598256</v>
+        <v>36.03985</v>
       </c>
       <c r="N26">
-        <v>359.801744</v>
+        <v>358.36015</v>
       </c>
       <c r="O26">
-        <v>89.950436</v>
+        <v>89.59003749999999</v>
       </c>
       <c r="P26">
-        <v>269.851308</v>
+        <v>268.7701125</v>
       </c>
       <c r="Q26">
-        <v>422.951308</v>
+        <v>421.8701125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1080851269173385</v>
+        <v>0.1087477346505017</v>
       </c>
       <c r="T26">
-        <v>1.214053054864694</v>
+        <v>1.22696851289517</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.39941851404302</v>
+        <v>10.9434417734813</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0912733009878763</v>
+        <v>0.09107790551857528</v>
       </c>
       <c r="C27">
-        <v>2069.912527570331</v>
+        <v>2051.795195499116</v>
       </c>
       <c r="D27">
-        <v>2250.662527570331</v>
+        <v>2260.375195499116</v>
       </c>
       <c r="E27">
-        <v>-269.45</v>
+        <v>-241.62</v>
       </c>
       <c r="F27">
-        <v>695.75</v>
+        <v>723.58</v>
       </c>
       <c r="G27">
         <v>515</v>
@@ -3501,28 +3501,28 @@
         <v>394.4</v>
       </c>
       <c r="M27">
-        <v>36.03985</v>
+        <v>37.481444</v>
       </c>
       <c r="N27">
-        <v>358.36015</v>
+        <v>356.918556</v>
       </c>
       <c r="O27">
-        <v>89.59003749999999</v>
+        <v>89.22963899999999</v>
       </c>
       <c r="P27">
-        <v>268.7701125</v>
+        <v>267.6889169999999</v>
       </c>
       <c r="Q27">
-        <v>421.8701125</v>
+        <v>420.788917</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1087477346505017</v>
+        <v>0.1094282507007774</v>
       </c>
       <c r="T27">
-        <v>1.22696851289517</v>
+        <v>1.240233037358901</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.9434417734813</v>
+        <v>10.52254016680894</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09107790551857528</v>
+        <v>0.09088251004927429</v>
       </c>
       <c r="C28">
-        <v>2051.795195499116</v>
+        <v>2033.762056224886</v>
       </c>
       <c r="D28">
-        <v>2260.375195499116</v>
+        <v>2270.172056224886</v>
       </c>
       <c r="E28">
-        <v>-241.62</v>
+        <v>-213.79</v>
       </c>
       <c r="F28">
-        <v>723.58</v>
+        <v>751.4100000000001</v>
       </c>
       <c r="G28">
         <v>515</v>
@@ -3583,28 +3583,28 @@
         <v>394.4</v>
       </c>
       <c r="M28">
-        <v>37.481444</v>
+        <v>38.92303800000001</v>
       </c>
       <c r="N28">
-        <v>356.918556</v>
+        <v>355.476962</v>
       </c>
       <c r="O28">
-        <v>89.22963899999999</v>
+        <v>88.86924049999999</v>
       </c>
       <c r="P28">
-        <v>267.6889169999999</v>
+        <v>266.6077215</v>
       </c>
       <c r="Q28">
-        <v>420.788917</v>
+        <v>419.7077215</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1094282507007774</v>
+        <v>0.1101274110264031</v>
       </c>
       <c r="T28">
-        <v>1.240233037358901</v>
+        <v>1.253860973451776</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.52254016680894</v>
+        <v>10.13281645692713</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09088251004927429</v>
+        <v>0.09104411457997327</v>
       </c>
       <c r="C29">
-        <v>2033.762056224886</v>
+        <v>1997.823375280236</v>
       </c>
       <c r="D29">
-        <v>2270.172056224886</v>
+        <v>2262.063375280236</v>
       </c>
       <c r="E29">
-        <v>-213.79</v>
+        <v>-185.9599999999999</v>
       </c>
       <c r="F29">
-        <v>751.4100000000001</v>
+        <v>779.2400000000001</v>
       </c>
       <c r="G29">
         <v>515</v>
@@ -3665,45 +3665,45 @@
         <v>394.4</v>
       </c>
       <c r="M29">
-        <v>38.92303800000001</v>
+        <v>41.68934000000001</v>
       </c>
       <c r="N29">
-        <v>355.476962</v>
+        <v>352.71066</v>
       </c>
       <c r="O29">
-        <v>88.86924049999999</v>
+        <v>88.17766499999999</v>
       </c>
       <c r="P29">
-        <v>266.6077215</v>
+        <v>264.532995</v>
       </c>
       <c r="Q29">
-        <v>419.7077215</v>
+        <v>417.632995</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1101274110264031</v>
+        <v>0.1108459924721851</v>
       </c>
       <c r="T29">
-        <v>1.253860973451776</v>
+        <v>1.267867463325009</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>10.13281645692713</v>
+        <v>9.460452000439439</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09104411457997327</v>
+        <v>0.09086146911067226</v>
       </c>
       <c r="C30">
-        <v>1997.823375280236</v>
+        <v>1979.162087151391</v>
       </c>
       <c r="D30">
-        <v>2262.063375280236</v>
+        <v>2271.232087151391</v>
       </c>
       <c r="E30">
-        <v>-185.9599999999999</v>
+        <v>-158.13</v>
       </c>
       <c r="F30">
-        <v>779.2400000000001</v>
+        <v>807.0700000000001</v>
       </c>
       <c r="G30">
         <v>515</v>
@@ -3747,28 +3747,28 @@
         <v>394.4</v>
       </c>
       <c r="M30">
-        <v>41.68934000000001</v>
+        <v>43.178245</v>
       </c>
       <c r="N30">
-        <v>352.71066</v>
+        <v>351.221755</v>
       </c>
       <c r="O30">
-        <v>88.17766499999999</v>
+        <v>87.80543874999999</v>
       </c>
       <c r="P30">
-        <v>264.532995</v>
+        <v>263.41631625</v>
       </c>
       <c r="Q30">
-        <v>417.632995</v>
+        <v>416.51631625</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1108459924721851</v>
+        <v>0.1115848156488342</v>
       </c>
       <c r="T30">
-        <v>1.267867463325009</v>
+        <v>1.282268502208755</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.460452000439439</v>
+        <v>9.134229517665666</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09086146911067226</v>
+        <v>0.09067882364137125</v>
       </c>
       <c r="C31">
-        <v>1979.162087151391</v>
+        <v>1960.575427702476</v>
       </c>
       <c r="D31">
-        <v>2271.232087151391</v>
+        <v>2280.475427702476</v>
       </c>
       <c r="E31">
-        <v>-158.1300000000001</v>
+        <v>-130.3000000000001</v>
       </c>
       <c r="F31">
-        <v>807.0699999999999</v>
+        <v>834.9</v>
       </c>
       <c r="G31">
         <v>515</v>
@@ -3829,28 +3829,28 @@
         <v>394.4</v>
       </c>
       <c r="M31">
-        <v>43.178245</v>
+        <v>44.66715</v>
       </c>
       <c r="N31">
-        <v>351.221755</v>
+        <v>349.73285</v>
       </c>
       <c r="O31">
-        <v>87.80543874999999</v>
+        <v>87.4332125</v>
       </c>
       <c r="P31">
-        <v>263.41631625</v>
+        <v>262.2996375</v>
       </c>
       <c r="Q31">
-        <v>416.51631625</v>
+        <v>415.3996375</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1115848156488342</v>
+        <v>0.1123447480591018</v>
       </c>
       <c r="T31">
-        <v>1.282268502208755</v>
+        <v>1.297080999346322</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.134229517665666</v>
+        <v>8.829755200410144</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09067882364137125</v>
+        <v>0.09049617817207026</v>
       </c>
       <c r="C32">
-        <v>1960.575427702476</v>
+        <v>1942.064311816429</v>
       </c>
       <c r="D32">
-        <v>2280.475427702476</v>
+        <v>2289.794311816429</v>
       </c>
       <c r="E32">
-        <v>-130.3000000000001</v>
+        <v>-102.47</v>
       </c>
       <c r="F32">
-        <v>834.9</v>
+        <v>862.73</v>
       </c>
       <c r="G32">
         <v>515</v>
@@ -3911,28 +3911,28 @@
         <v>394.4</v>
       </c>
       <c r="M32">
-        <v>44.66715</v>
+        <v>46.156055</v>
       </c>
       <c r="N32">
-        <v>349.73285</v>
+        <v>348.243945</v>
       </c>
       <c r="O32">
-        <v>87.4332125</v>
+        <v>87.06098625</v>
       </c>
       <c r="P32">
-        <v>262.2996375</v>
+        <v>261.18295875</v>
       </c>
       <c r="Q32">
-        <v>415.3996375</v>
+        <v>414.28295875</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1123447480591018</v>
+        <v>0.113126707495754</v>
       </c>
       <c r="T32">
-        <v>1.297080999346322</v>
+        <v>1.312322844227008</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.829755200410144</v>
+        <v>8.544924387493687</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09049617817207026</v>
+        <v>0.09031353270276926</v>
       </c>
       <c r="C33">
-        <v>1942.064311816429</v>
+        <v>1923.629669391777</v>
       </c>
       <c r="D33">
-        <v>2289.794311816429</v>
+        <v>2299.189669391777</v>
       </c>
       <c r="E33">
-        <v>-102.47</v>
+        <v>-74.63999999999999</v>
       </c>
       <c r="F33">
-        <v>862.73</v>
+        <v>890.5600000000001</v>
       </c>
       <c r="G33">
         <v>515</v>
@@ -3993,28 +3993,28 @@
         <v>394.4</v>
       </c>
       <c r="M33">
-        <v>46.156055</v>
+        <v>47.64496</v>
       </c>
       <c r="N33">
-        <v>348.243945</v>
+        <v>346.75504</v>
       </c>
       <c r="O33">
-        <v>87.06098625</v>
+        <v>86.68875999999999</v>
       </c>
       <c r="P33">
-        <v>261.18295875</v>
+        <v>260.0662799999999</v>
       </c>
       <c r="Q33">
-        <v>414.28295875</v>
+        <v>413.16628</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.113126707495754</v>
+        <v>0.1139316657393666</v>
       </c>
       <c r="T33">
-        <v>1.312322844227008</v>
+        <v>1.328012978663007</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.544924387493687</v>
+        <v>8.27789550038451</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09031353270276926</v>
+        <v>0.09013088723346825</v>
       </c>
       <c r="C34">
-        <v>1923.629669391777</v>
+        <v>1905.272445651961</v>
       </c>
       <c r="D34">
-        <v>2299.189669391777</v>
+        <v>2308.662445651961</v>
       </c>
       <c r="E34">
-        <v>-74.63999999999999</v>
+        <v>-46.80999999999995</v>
       </c>
       <c r="F34">
-        <v>890.5600000000001</v>
+        <v>918.3900000000001</v>
       </c>
       <c r="G34">
         <v>515</v>
@@ -4075,28 +4075,28 @@
         <v>394.4</v>
       </c>
       <c r="M34">
-        <v>47.64496</v>
+        <v>49.13386500000001</v>
       </c>
       <c r="N34">
-        <v>346.75504</v>
+        <v>345.266135</v>
       </c>
       <c r="O34">
-        <v>86.68875999999999</v>
+        <v>86.31653374999999</v>
       </c>
       <c r="P34">
-        <v>260.0662799999999</v>
+        <v>258.94960125</v>
       </c>
       <c r="Q34">
-        <v>413.16628</v>
+        <v>412.04960125</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1139316657393666</v>
+        <v>0.1147606525872661</v>
       </c>
       <c r="T34">
-        <v>1.328012978663007</v>
+        <v>1.344171475320977</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.27789550038451</v>
+        <v>8.02705018219104</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09013088723346825</v>
+        <v>0.08994824176416724</v>
       </c>
       <c r="C35">
-        <v>1905.272445651961</v>
+        <v>1886.993601462337</v>
       </c>
       <c r="D35">
-        <v>2308.662445651961</v>
+        <v>2318.213601462337</v>
       </c>
       <c r="E35">
-        <v>-46.80999999999995</v>
+        <v>-18.98000000000002</v>
       </c>
       <c r="F35">
-        <v>918.3900000000001</v>
+        <v>946.22</v>
       </c>
       <c r="G35">
         <v>515</v>
@@ -4157,28 +4157,28 @@
         <v>394.4</v>
       </c>
       <c r="M35">
-        <v>49.13386500000001</v>
+        <v>50.62277</v>
       </c>
       <c r="N35">
-        <v>345.266135</v>
+        <v>343.77723</v>
       </c>
       <c r="O35">
-        <v>86.31653374999999</v>
+        <v>85.94430749999999</v>
       </c>
       <c r="P35">
-        <v>258.94960125</v>
+        <v>257.8329225</v>
       </c>
       <c r="Q35">
-        <v>412.04960125</v>
+        <v>410.9329225</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1147606525872661</v>
+        <v>0.1156147602487383</v>
       </c>
       <c r="T35">
-        <v>1.344171475320977</v>
+        <v>1.360819623392825</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.02705018219104</v>
+        <v>7.790960470950127</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08994824176416724</v>
+        <v>0.08997559629486623</v>
       </c>
       <c r="C36">
-        <v>1886.993601462337</v>
+        <v>1857.728111045756</v>
       </c>
       <c r="D36">
-        <v>2318.213601462337</v>
+        <v>2316.778111045756</v>
       </c>
       <c r="E36">
-        <v>-18.98000000000002</v>
+        <v>8.850000000000023</v>
       </c>
       <c r="F36">
-        <v>946.22</v>
+        <v>974.0500000000001</v>
       </c>
       <c r="G36">
         <v>515</v>
@@ -4239,45 +4239,45 @@
         <v>394.4</v>
       </c>
       <c r="M36">
-        <v>50.62277</v>
+        <v>52.89091500000001</v>
       </c>
       <c r="N36">
-        <v>343.77723</v>
+        <v>341.509085</v>
       </c>
       <c r="O36">
-        <v>85.94430749999999</v>
+        <v>85.37727124999999</v>
       </c>
       <c r="P36">
-        <v>257.8329225</v>
+        <v>256.13181375</v>
       </c>
       <c r="Q36">
-        <v>410.9329225</v>
+        <v>409.23181375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1156147602487383</v>
+        <v>0.1164951481459481</v>
       </c>
       <c r="T36">
-        <v>1.360819623392825</v>
+        <v>1.377980022174575</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.790960470950127</v>
+        <v>7.456857193716537</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08997559629486623</v>
+        <v>0.08979895082556524</v>
       </c>
       <c r="C37">
-        <v>1857.728111045756</v>
+        <v>1839.1994318503</v>
       </c>
       <c r="D37">
-        <v>2316.778111045756</v>
+        <v>2326.0794318503</v>
       </c>
       <c r="E37">
-        <v>8.850000000000023</v>
+        <v>36.68000000000006</v>
       </c>
       <c r="F37">
-        <v>974.0500000000001</v>
+        <v>1001.88</v>
       </c>
       <c r="G37">
         <v>515</v>
@@ -4321,28 +4321,28 @@
         <v>394.4</v>
       </c>
       <c r="M37">
-        <v>52.89091500000001</v>
+        <v>54.40208400000001</v>
       </c>
       <c r="N37">
-        <v>341.509085</v>
+        <v>339.997916</v>
       </c>
       <c r="O37">
-        <v>85.37727124999999</v>
+        <v>84.99947899999999</v>
       </c>
       <c r="P37">
-        <v>256.13181375</v>
+        <v>254.998437</v>
       </c>
       <c r="Q37">
-        <v>409.23181375</v>
+        <v>408.098437</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1164951481459481</v>
+        <v>0.1174030481649457</v>
       </c>
       <c r="T37">
-        <v>1.377980022174575</v>
+        <v>1.395676683418256</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.456857193716537</v>
+        <v>7.249722271668856</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08979895082556524</v>
+        <v>0.08962230535626425</v>
       </c>
       <c r="C38">
-        <v>1839.1994318503</v>
+        <v>1820.745738950763</v>
       </c>
       <c r="D38">
-        <v>2326.0794318503</v>
+        <v>2335.455738950763</v>
       </c>
       <c r="E38">
-        <v>36.67999999999995</v>
+        <v>64.50999999999999</v>
       </c>
       <c r="F38">
-        <v>1001.88</v>
+        <v>1029.71</v>
       </c>
       <c r="G38">
         <v>515</v>
@@ -4403,28 +4403,28 @@
         <v>394.4</v>
       </c>
       <c r="M38">
-        <v>54.402084</v>
+        <v>55.913253</v>
       </c>
       <c r="N38">
-        <v>339.997916</v>
+        <v>338.486747</v>
       </c>
       <c r="O38">
-        <v>84.99947899999999</v>
+        <v>84.62168674999999</v>
       </c>
       <c r="P38">
-        <v>254.998437</v>
+        <v>253.86506025</v>
       </c>
       <c r="Q38">
-        <v>408.098437</v>
+        <v>406.96506025</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1174030481649457</v>
+        <v>0.1183397704067687</v>
       </c>
       <c r="T38">
-        <v>1.395676683418256</v>
+        <v>1.413935143431577</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.249722271668857</v>
+        <v>7.053783831894022</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08962230535626425</v>
+        <v>0.08944565988696324</v>
       </c>
       <c r="C39">
-        <v>1820.745738950763</v>
+        <v>1802.367942814953</v>
       </c>
       <c r="D39">
-        <v>2335.455738950763</v>
+        <v>2344.907942814953</v>
       </c>
       <c r="E39">
-        <v>64.50999999999999</v>
+        <v>92.33999999999992</v>
       </c>
       <c r="F39">
-        <v>1029.71</v>
+        <v>1057.54</v>
       </c>
       <c r="G39">
         <v>515</v>
@@ -4485,28 +4485,28 @@
         <v>394.4</v>
       </c>
       <c r="M39">
-        <v>55.913253</v>
+        <v>57.424422</v>
       </c>
       <c r="N39">
-        <v>338.486747</v>
+        <v>336.975578</v>
       </c>
       <c r="O39">
-        <v>84.62168674999999</v>
+        <v>84.2438945</v>
       </c>
       <c r="P39">
-        <v>253.86506025</v>
+        <v>252.7316835</v>
       </c>
       <c r="Q39">
-        <v>406.96506025</v>
+        <v>405.8316835</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1183397704067687</v>
+        <v>0.119306709495102</v>
       </c>
       <c r="T39">
-        <v>1.413935143431577</v>
+        <v>1.432782586025973</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.053783831894022</v>
+        <v>6.868157941581022</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08944565988696324</v>
+        <v>0.08926901441766225</v>
       </c>
       <c r="C40">
-        <v>1802.367942814953</v>
+        <v>1784.066968710187</v>
       </c>
       <c r="D40">
-        <v>2344.907942814953</v>
+        <v>2354.436968710187</v>
       </c>
       <c r="E40">
-        <v>92.33999999999992</v>
+        <v>120.1700000000001</v>
       </c>
       <c r="F40">
-        <v>1057.54</v>
+        <v>1085.37</v>
       </c>
       <c r="G40">
         <v>515</v>
@@ -4567,28 +4567,28 @@
         <v>394.4</v>
       </c>
       <c r="M40">
-        <v>57.424422</v>
+        <v>58.93559100000001</v>
       </c>
       <c r="N40">
-        <v>336.975578</v>
+        <v>335.464409</v>
       </c>
       <c r="O40">
-        <v>84.2438945</v>
+        <v>83.86610225</v>
       </c>
       <c r="P40">
-        <v>252.7316835</v>
+        <v>251.59830675</v>
       </c>
       <c r="Q40">
-        <v>405.8316835</v>
+        <v>404.69830675</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.119306709495102</v>
+        <v>0.1203053515043643</v>
       </c>
       <c r="T40">
-        <v>1.432782586025973</v>
+        <v>1.45224797755789</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.868157941581022</v>
+        <v>6.692051327694329</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08926901441766225</v>
+        <v>0.08909236894836123</v>
       </c>
       <c r="C41">
-        <v>1784.066968710187</v>
+        <v>1765.843757005222</v>
       </c>
       <c r="D41">
-        <v>2354.436968710187</v>
+        <v>2364.043757005222</v>
       </c>
       <c r="E41">
-        <v>120.1700000000001</v>
+        <v>148</v>
       </c>
       <c r="F41">
-        <v>1085.37</v>
+        <v>1113.2</v>
       </c>
       <c r="G41">
         <v>515</v>
@@ -4649,28 +4649,28 @@
         <v>394.4</v>
       </c>
       <c r="M41">
-        <v>58.93559100000001</v>
+        <v>60.44676</v>
       </c>
       <c r="N41">
-        <v>335.464409</v>
+        <v>333.95324</v>
       </c>
       <c r="O41">
-        <v>83.86610225</v>
+        <v>83.48831</v>
       </c>
       <c r="P41">
-        <v>251.59830675</v>
+        <v>250.46493</v>
       </c>
       <c r="Q41">
-        <v>404.69830675</v>
+        <v>403.56493</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1203053515043643</v>
+        <v>0.1213372815806021</v>
       </c>
       <c r="T41">
-        <v>1.45224797755789</v>
+        <v>1.472362215474204</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.692051327694329</v>
+        <v>6.524750044501971</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08909236894836123</v>
+        <v>0.08891572347906024</v>
       </c>
       <c r="C42">
-        <v>1765.843757005222</v>
+        <v>1747.699263479607</v>
       </c>
       <c r="D42">
-        <v>2364.043757005222</v>
+        <v>2373.729263479608</v>
       </c>
       <c r="E42">
-        <v>148</v>
+        <v>175.8300000000002</v>
       </c>
       <c r="F42">
-        <v>1113.2</v>
+        <v>1141.03</v>
       </c>
       <c r="G42">
         <v>515</v>
@@ -4731,28 +4731,28 @@
         <v>394.4</v>
       </c>
       <c r="M42">
-        <v>60.44676</v>
+        <v>61.95792900000001</v>
       </c>
       <c r="N42">
-        <v>333.95324</v>
+        <v>332.4420709999999</v>
       </c>
       <c r="O42">
-        <v>83.48831</v>
+        <v>83.11051774999999</v>
       </c>
       <c r="P42">
-        <v>250.46493</v>
+        <v>249.33155325</v>
       </c>
       <c r="Q42">
-        <v>403.56493</v>
+        <v>402.43155325</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1213372815806021</v>
+        <v>0.1224041923373902</v>
       </c>
       <c r="T42">
-        <v>1.472362215474204</v>
+        <v>1.493158291963953</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.524750044501971</v>
+        <v>6.365609799514116</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08891572347906024</v>
+        <v>0.08873907800975925</v>
       </c>
       <c r="C43">
-        <v>1747.699263479607</v>
+        <v>1729.634459640679</v>
       </c>
       <c r="D43">
-        <v>2373.729263479608</v>
+        <v>2383.494459640679</v>
       </c>
       <c r="E43">
-        <v>175.8300000000002</v>
+        <v>203.6600000000001</v>
       </c>
       <c r="F43">
-        <v>1141.03</v>
+        <v>1168.86</v>
       </c>
       <c r="G43">
         <v>515</v>
@@ -4813,28 +4813,28 @@
         <v>394.4</v>
       </c>
       <c r="M43">
-        <v>61.95792900000001</v>
+        <v>63.46909800000001</v>
       </c>
       <c r="N43">
-        <v>332.4420709999999</v>
+        <v>330.9309019999999</v>
       </c>
       <c r="O43">
-        <v>83.11051774999999</v>
+        <v>82.73272549999999</v>
       </c>
       <c r="P43">
-        <v>249.33155325</v>
+        <v>248.1981765</v>
       </c>
       <c r="Q43">
-        <v>402.43155325</v>
+        <v>401.2981765</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1224041923373902</v>
+        <v>0.1235078931202745</v>
       </c>
       <c r="T43">
-        <v>1.493158291963953</v>
+        <v>1.514671474539555</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.365609799514116</v>
+        <v>6.214047661430447</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08873907800975925</v>
+        <v>0.08888493254045822</v>
       </c>
       <c r="C44">
-        <v>1729.63445964068</v>
+        <v>1693.735665161124</v>
       </c>
       <c r="D44">
-        <v>2383.494459640679</v>
+        <v>2375.425665161124</v>
       </c>
       <c r="E44">
-        <v>203.6599999999999</v>
+        <v>231.49</v>
       </c>
       <c r="F44">
-        <v>1168.86</v>
+        <v>1196.69</v>
       </c>
       <c r="G44">
         <v>515</v>
@@ -4895,45 +4895,45 @@
         <v>394.4</v>
       </c>
       <c r="M44">
-        <v>63.469098</v>
+        <v>66.176957</v>
       </c>
       <c r="N44">
-        <v>330.930902</v>
+        <v>328.223043</v>
       </c>
       <c r="O44">
-        <v>82.7327255</v>
+        <v>82.05576074999999</v>
       </c>
       <c r="P44">
-        <v>248.1981765</v>
+        <v>246.16728225</v>
       </c>
       <c r="Q44">
-        <v>401.2981765</v>
+        <v>399.26728225</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1235078931202745</v>
+        <v>0.1246503202464179</v>
       </c>
       <c r="T44">
-        <v>1.514671474539555</v>
+        <v>1.536939505626581</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.21404766143045</v>
+        <v>5.959778416526465</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08888493254045822</v>
+        <v>0.08871578707115724</v>
       </c>
       <c r="C45">
-        <v>1693.735665161124</v>
+        <v>1675.268012128152</v>
       </c>
       <c r="D45">
-        <v>2375.425665161124</v>
+        <v>2384.788012128152</v>
       </c>
       <c r="E45">
-        <v>231.49</v>
+        <v>259.3199999999999</v>
       </c>
       <c r="F45">
-        <v>1196.69</v>
+        <v>1224.52</v>
       </c>
       <c r="G45">
         <v>515</v>
@@ -4977,28 +4977,28 @@
         <v>394.4</v>
       </c>
       <c r="M45">
-        <v>66.176957</v>
+        <v>67.71595600000001</v>
       </c>
       <c r="N45">
-        <v>328.223043</v>
+        <v>326.684044</v>
       </c>
       <c r="O45">
-        <v>82.05576074999999</v>
+        <v>81.67101099999999</v>
       </c>
       <c r="P45">
-        <v>246.16728225</v>
+        <v>245.013033</v>
       </c>
       <c r="Q45">
-        <v>399.26728225</v>
+        <v>398.113033</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1246503202464179</v>
+        <v>0.1258335483413522</v>
       </c>
       <c r="T45">
-        <v>1.536939505626581</v>
+        <v>1.560002823538145</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.959778416526465</v>
+        <v>5.824328907059954</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08871578707115724</v>
+        <v>0.08854664160185621</v>
       </c>
       <c r="C46">
-        <v>1675.268012128152</v>
+        <v>1656.874451398678</v>
       </c>
       <c r="D46">
-        <v>2384.788012128152</v>
+        <v>2394.224451398678</v>
       </c>
       <c r="E46">
-        <v>259.3199999999999</v>
+        <v>287.1500000000001</v>
       </c>
       <c r="F46">
-        <v>1224.52</v>
+        <v>1252.35</v>
       </c>
       <c r="G46">
         <v>515</v>
@@ -5059,28 +5059,28 @@
         <v>394.4</v>
       </c>
       <c r="M46">
-        <v>67.71595600000001</v>
+        <v>69.25495500000001</v>
       </c>
       <c r="N46">
-        <v>326.684044</v>
+        <v>325.145045</v>
       </c>
       <c r="O46">
-        <v>81.67101099999999</v>
+        <v>81.28626125</v>
       </c>
       <c r="P46">
-        <v>245.013033</v>
+        <v>243.85878375</v>
       </c>
       <c r="Q46">
-        <v>398.113033</v>
+        <v>396.95878375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1258335483413522</v>
+        <v>0.1270598029124659</v>
       </c>
       <c r="T46">
-        <v>1.560002823538145</v>
+        <v>1.583904807555583</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.824328907059954</v>
+        <v>5.694899375791955</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08854664160185621</v>
+        <v>0.08837749613255522</v>
       </c>
       <c r="C47">
-        <v>1656.874451398678</v>
+        <v>1638.555866000959</v>
       </c>
       <c r="D47">
-        <v>2394.224451398678</v>
+        <v>2403.735866000959</v>
       </c>
       <c r="E47">
-        <v>287.1500000000001</v>
+        <v>314.98</v>
       </c>
       <c r="F47">
-        <v>1252.35</v>
+        <v>1280.18</v>
       </c>
       <c r="G47">
         <v>515</v>
@@ -5141,28 +5141,28 @@
         <v>394.4</v>
       </c>
       <c r="M47">
-        <v>69.25495500000001</v>
+        <v>70.793954</v>
       </c>
       <c r="N47">
-        <v>325.145045</v>
+        <v>323.606046</v>
       </c>
       <c r="O47">
-        <v>81.28626125</v>
+        <v>80.9015115</v>
       </c>
       <c r="P47">
-        <v>243.85878375</v>
+        <v>242.7045345</v>
       </c>
       <c r="Q47">
-        <v>396.95878375</v>
+        <v>395.8045345</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1270598029124659</v>
+        <v>0.1283314743195467</v>
       </c>
       <c r="T47">
-        <v>1.583904807555583</v>
+        <v>1.608692050240334</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.694899375791955</v>
+        <v>5.571097215448653</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08837749613255522</v>
+        <v>0.08820835066325422</v>
       </c>
       <c r="C48">
-        <v>1638.555866000959</v>
+        <v>1620.31315305107</v>
       </c>
       <c r="D48">
-        <v>2403.735866000959</v>
+        <v>2413.32315305107</v>
       </c>
       <c r="E48">
-        <v>314.98</v>
+        <v>342.8099999999999</v>
       </c>
       <c r="F48">
-        <v>1280.18</v>
+        <v>1308.01</v>
       </c>
       <c r="G48">
         <v>515</v>
@@ -5223,28 +5223,28 @@
         <v>394.4</v>
       </c>
       <c r="M48">
-        <v>70.793954</v>
+        <v>72.332953</v>
       </c>
       <c r="N48">
-        <v>323.606046</v>
+        <v>322.067047</v>
       </c>
       <c r="O48">
-        <v>80.9015115</v>
+        <v>80.51676175</v>
       </c>
       <c r="P48">
-        <v>242.7045345</v>
+        <v>241.55028525</v>
       </c>
       <c r="Q48">
-        <v>395.8045345</v>
+        <v>394.65028525</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1283314743195467</v>
+        <v>0.1296511333268947</v>
       </c>
       <c r="T48">
-        <v>1.608692050240334</v>
+        <v>1.634414660573566</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.571097215448653</v>
+        <v>5.452563232141234</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08820835066325422</v>
+        <v>0.08803920519395322</v>
       </c>
       <c r="C49">
-        <v>1620.31315305107</v>
+        <v>1602.147224034967</v>
       </c>
       <c r="D49">
-        <v>2413.32315305107</v>
+        <v>2422.987224034967</v>
       </c>
       <c r="E49">
-        <v>342.8099999999999</v>
+        <v>370.6400000000001</v>
       </c>
       <c r="F49">
-        <v>1308.01</v>
+        <v>1335.84</v>
       </c>
       <c r="G49">
         <v>515</v>
@@ -5305,28 +5305,28 @@
         <v>394.4</v>
       </c>
       <c r="M49">
-        <v>72.332953</v>
+        <v>73.87195200000001</v>
       </c>
       <c r="N49">
-        <v>322.067047</v>
+        <v>320.528048</v>
       </c>
       <c r="O49">
-        <v>80.51676175</v>
+        <v>80.13201199999999</v>
       </c>
       <c r="P49">
-        <v>241.55028525</v>
+        <v>240.396036</v>
       </c>
       <c r="Q49">
-        <v>394.65028525</v>
+        <v>393.496036</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1296511333268947</v>
+        <v>0.13102154844991</v>
       </c>
       <c r="T49">
-        <v>1.634414660573566</v>
+        <v>1.661126602073461</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.452563232141234</v>
+        <v>5.338968164804958</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08803920519395321</v>
+        <v>0.08787005972465221</v>
       </c>
       <c r="C50">
-        <v>1602.147224034968</v>
+        <v>1584.05900509737</v>
       </c>
       <c r="D50">
-        <v>2422.987224034968</v>
+        <v>2432.72900509737</v>
       </c>
       <c r="E50">
-        <v>370.6399999999999</v>
+        <v>398.47</v>
       </c>
       <c r="F50">
-        <v>1335.84</v>
+        <v>1363.67</v>
       </c>
       <c r="G50">
         <v>515</v>
@@ -5387,28 +5387,28 @@
         <v>394.4</v>
       </c>
       <c r="M50">
-        <v>73.87195199999999</v>
+        <v>75.41095100000001</v>
       </c>
       <c r="N50">
-        <v>320.528048</v>
+        <v>318.989049</v>
       </c>
       <c r="O50">
-        <v>80.132012</v>
+        <v>79.74726224999999</v>
       </c>
       <c r="P50">
-        <v>240.396036</v>
+        <v>239.24178675</v>
       </c>
       <c r="Q50">
-        <v>393.496036</v>
+        <v>392.34178675</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.13102154844991</v>
+        <v>0.1324457053424553</v>
       </c>
       <c r="T50">
-        <v>1.661126602073461</v>
+        <v>1.688886070690998</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.338968164804959</v>
+        <v>5.230009630829346</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08787005972465221</v>
+        <v>0.0877009142553512</v>
       </c>
       <c r="C51">
-        <v>1584.05900509737</v>
+        <v>1566.049437337624</v>
       </c>
       <c r="D51">
-        <v>2432.72900509737</v>
+        <v>2442.549437337624</v>
       </c>
       <c r="E51">
-        <v>398.47</v>
+        <v>426.3</v>
       </c>
       <c r="F51">
-        <v>1363.67</v>
+        <v>1391.5</v>
       </c>
       <c r="G51">
         <v>515</v>
@@ -5469,28 +5469,28 @@
         <v>394.4</v>
       </c>
       <c r="M51">
-        <v>75.41095100000001</v>
+        <v>76.94995</v>
       </c>
       <c r="N51">
-        <v>318.989049</v>
+        <v>317.45005</v>
       </c>
       <c r="O51">
-        <v>79.74726224999999</v>
+        <v>79.36251249999999</v>
       </c>
       <c r="P51">
-        <v>239.24178675</v>
+        <v>238.0875375</v>
       </c>
       <c r="Q51">
-        <v>392.34178675</v>
+        <v>391.1875375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1324457053424553</v>
+        <v>0.1339268285107024</v>
       </c>
       <c r="T51">
-        <v>1.688886070690998</v>
+        <v>1.717755918053238</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.230009630829346</v>
+        <v>5.12540943821276</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0877009142553512</v>
+        <v>0.08753176878605021</v>
       </c>
       <c r="C52">
-        <v>1566.049437337624</v>
+        <v>1548.119477112776</v>
       </c>
       <c r="D52">
-        <v>2442.549437337624</v>
+        <v>2452.449477112776</v>
       </c>
       <c r="E52">
-        <v>426.3</v>
+        <v>454.1299999999999</v>
       </c>
       <c r="F52">
-        <v>1391.5</v>
+        <v>1419.33</v>
       </c>
       <c r="G52">
         <v>515</v>
@@ -5551,28 +5551,28 @@
         <v>394.4</v>
       </c>
       <c r="M52">
-        <v>76.94995</v>
+        <v>78.48894900000001</v>
       </c>
       <c r="N52">
-        <v>317.45005</v>
+        <v>315.911051</v>
       </c>
       <c r="O52">
-        <v>79.36251249999999</v>
+        <v>78.97776275</v>
       </c>
       <c r="P52">
-        <v>238.0875375</v>
+        <v>236.93328825</v>
       </c>
       <c r="Q52">
-        <v>391.1875375</v>
+        <v>390.03328825</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1339268285107024</v>
+        <v>0.1354684056858168</v>
       </c>
       <c r="T52">
-        <v>1.717755918053238</v>
+        <v>1.747804126532303</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.12540943821276</v>
+        <v>5.024911213934078</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08753176878605021</v>
+        <v>0.0873626233167492</v>
       </c>
       <c r="C53">
-        <v>1548.119477112776</v>
+        <v>1530.270096348042</v>
       </c>
       <c r="D53">
-        <v>2452.449477112776</v>
+        <v>2462.430096348042</v>
       </c>
       <c r="E53">
-        <v>454.1299999999999</v>
+        <v>481.96</v>
       </c>
       <c r="F53">
-        <v>1419.33</v>
+        <v>1447.16</v>
       </c>
       <c r="G53">
         <v>515</v>
@@ -5633,28 +5633,28 @@
         <v>394.4</v>
       </c>
       <c r="M53">
-        <v>78.48894900000001</v>
+        <v>80.02794800000001</v>
       </c>
       <c r="N53">
-        <v>315.911051</v>
+        <v>314.3720519999999</v>
       </c>
       <c r="O53">
-        <v>78.97776275</v>
+        <v>78.59301299999998</v>
       </c>
       <c r="P53">
-        <v>236.93328825</v>
+        <v>235.779039</v>
       </c>
       <c r="Q53">
-        <v>390.03328825</v>
+        <v>388.879039</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1354684056858168</v>
+        <v>0.1370742152432275</v>
       </c>
       <c r="T53">
-        <v>1.747804126532303</v>
+        <v>1.779104343697996</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.024911213934078</v>
+        <v>4.928278305973807</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0873626233167492</v>
+        <v>0.08719347784744819</v>
       </c>
       <c r="C54">
-        <v>1530.270096348042</v>
+        <v>1512.502282854881</v>
       </c>
       <c r="D54">
-        <v>2462.430096348042</v>
+        <v>2472.492282854881</v>
       </c>
       <c r="E54">
-        <v>481.96</v>
+        <v>509.79</v>
       </c>
       <c r="F54">
-        <v>1447.16</v>
+        <v>1474.99</v>
       </c>
       <c r="G54">
         <v>515</v>
@@ -5715,28 +5715,28 @@
         <v>394.4</v>
       </c>
       <c r="M54">
-        <v>80.02794800000001</v>
+        <v>81.566947</v>
       </c>
       <c r="N54">
-        <v>314.3720519999999</v>
+        <v>312.8330529999999</v>
       </c>
       <c r="O54">
-        <v>78.59301299999998</v>
+        <v>78.20826324999999</v>
       </c>
       <c r="P54">
-        <v>235.779039</v>
+        <v>234.62478975</v>
       </c>
       <c r="Q54">
-        <v>388.879039</v>
+        <v>387.72478975</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1370742152432275</v>
+        <v>0.1387483571222302</v>
       </c>
       <c r="T54">
-        <v>1.779104343697996</v>
+        <v>1.8117364849984</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.928278305973807</v>
+        <v>4.835291922842226</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08719347784744819</v>
+        <v>0.08702433237814718</v>
       </c>
       <c r="C55">
-        <v>1512.502282854881</v>
+        <v>1494.817040656909</v>
       </c>
       <c r="D55">
-        <v>2472.492282854881</v>
+        <v>2482.637040656909</v>
       </c>
       <c r="E55">
-        <v>509.79</v>
+        <v>537.6200000000001</v>
       </c>
       <c r="F55">
-        <v>1474.99</v>
+        <v>1502.82</v>
       </c>
       <c r="G55">
         <v>515</v>
@@ -5797,28 +5797,28 @@
         <v>394.4</v>
       </c>
       <c r="M55">
-        <v>81.566947</v>
+        <v>83.10594600000002</v>
       </c>
       <c r="N55">
-        <v>312.8330529999999</v>
+        <v>311.294054</v>
       </c>
       <c r="O55">
-        <v>78.20826324999999</v>
+        <v>77.82351349999999</v>
       </c>
       <c r="P55">
-        <v>234.62478975</v>
+        <v>233.4705405</v>
       </c>
       <c r="Q55">
-        <v>387.72478975</v>
+        <v>386.5705405</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1387483571222302</v>
+        <v>0.1404952877785808</v>
       </c>
       <c r="T55">
-        <v>1.8117364849984</v>
+        <v>1.845787415050995</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.835291922842226</v>
+        <v>4.745749479826628</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08702433237814718</v>
+        <v>0.08685518690884618</v>
       </c>
       <c r="C56">
-        <v>1494.817040656909</v>
+        <v>1477.215390323866</v>
       </c>
       <c r="D56">
-        <v>2482.637040656909</v>
+        <v>2492.865390323866</v>
       </c>
       <c r="E56">
-        <v>537.6200000000001</v>
+        <v>565.45</v>
       </c>
       <c r="F56">
-        <v>1502.82</v>
+        <v>1530.65</v>
       </c>
       <c r="G56">
         <v>515</v>
@@ -5879,28 +5879,28 @@
         <v>394.4</v>
       </c>
       <c r="M56">
-        <v>83.10594600000002</v>
+        <v>84.64494500000001</v>
       </c>
       <c r="N56">
-        <v>311.294054</v>
+        <v>309.755055</v>
       </c>
       <c r="O56">
-        <v>77.82351349999999</v>
+        <v>77.43876374999999</v>
       </c>
       <c r="P56">
-        <v>233.4705405</v>
+        <v>232.31629125</v>
       </c>
       <c r="Q56">
-        <v>386.5705405</v>
+        <v>385.41629125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1404952877785808</v>
+        <v>0.142319859797436</v>
       </c>
       <c r="T56">
-        <v>1.845787415050995</v>
+        <v>1.881351719772594</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.745749479826628</v>
+        <v>4.659463125647964</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08685518690884618</v>
+        <v>0.08668604143954517</v>
       </c>
       <c r="C57">
-        <v>1477.215390323866</v>
+        <v>1459.698369313872</v>
       </c>
       <c r="D57">
-        <v>2492.865390323866</v>
+        <v>2503.178369313872</v>
       </c>
       <c r="E57">
-        <v>565.45</v>
+        <v>593.2800000000002</v>
       </c>
       <c r="F57">
-        <v>1530.65</v>
+        <v>1558.48</v>
       </c>
       <c r="G57">
         <v>515</v>
@@ -5961,28 +5961,28 @@
         <v>394.4</v>
       </c>
       <c r="M57">
-        <v>84.64494500000001</v>
+        <v>86.18394400000001</v>
       </c>
       <c r="N57">
-        <v>309.755055</v>
+        <v>308.216056</v>
       </c>
       <c r="O57">
-        <v>77.43876374999999</v>
+        <v>77.054014</v>
       </c>
       <c r="P57">
-        <v>232.31629125</v>
+        <v>231.162042</v>
       </c>
       <c r="Q57">
-        <v>385.41629125</v>
+        <v>384.262042</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.142319859797436</v>
+        <v>0.1442273669080572</v>
       </c>
       <c r="T57">
-        <v>1.881351719772594</v>
+        <v>1.91853258379972</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.659463125647964</v>
+        <v>4.576258426975678</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08668604143954517</v>
+        <v>0.08758564597024418</v>
       </c>
       <c r="C58">
-        <v>1459.698369313872</v>
+        <v>1377.977360813343</v>
       </c>
       <c r="D58">
-        <v>2503.178369313872</v>
+        <v>2449.287360813344</v>
       </c>
       <c r="E58">
-        <v>593.2800000000002</v>
+        <v>621.1100000000001</v>
       </c>
       <c r="F58">
-        <v>1558.48</v>
+        <v>1586.31</v>
       </c>
       <c r="G58">
         <v>515</v>
@@ -6043,45 +6043,45 @@
         <v>394.4</v>
       </c>
       <c r="M58">
-        <v>86.18394400000001</v>
+        <v>91.68871800000002</v>
       </c>
       <c r="N58">
-        <v>308.216056</v>
+        <v>302.711282</v>
       </c>
       <c r="O58">
-        <v>77.054014</v>
+        <v>75.6778205</v>
       </c>
       <c r="P58">
-        <v>231.162042</v>
+        <v>227.0334615</v>
       </c>
       <c r="Q58">
-        <v>384.262042</v>
+        <v>380.1334615</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1442273669080572</v>
+        <v>0.1462235952796376</v>
       </c>
       <c r="T58">
-        <v>1.91853258379972</v>
+        <v>1.957442790339736</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.576258426975678</v>
+        <v>4.301510683135518</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08758564597024418</v>
+        <v>0.08743525050094317</v>
       </c>
       <c r="C59">
-        <v>1377.977360813343</v>
+        <v>1358.994712940461</v>
       </c>
       <c r="D59">
-        <v>2449.287360813344</v>
+        <v>2458.134712940461</v>
       </c>
       <c r="E59">
-        <v>621.1100000000001</v>
+        <v>648.9400000000001</v>
       </c>
       <c r="F59">
-        <v>1586.31</v>
+        <v>1614.14</v>
       </c>
       <c r="G59">
         <v>515</v>
@@ -6125,28 +6125,28 @@
         <v>394.4</v>
       </c>
       <c r="M59">
-        <v>91.68871800000002</v>
+        <v>93.29729200000001</v>
       </c>
       <c r="N59">
-        <v>302.711282</v>
+        <v>301.102708</v>
       </c>
       <c r="O59">
-        <v>75.6778205</v>
+        <v>75.27567699999999</v>
       </c>
       <c r="P59">
-        <v>227.0334615</v>
+        <v>225.827031</v>
       </c>
       <c r="Q59">
-        <v>380.1334615</v>
+        <v>378.927031</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1462235952796376</v>
+        <v>0.1483148821451028</v>
       </c>
       <c r="T59">
-        <v>1.957442790339736</v>
+        <v>1.998205863857848</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.301510683135518</v>
+        <v>4.227346705840079</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08743525050094317</v>
+        <v>0.08728485503164217</v>
       </c>
       <c r="C60">
-        <v>1358.994712940461</v>
+        <v>1340.076213859912</v>
       </c>
       <c r="D60">
-        <v>2458.134712940461</v>
+        <v>2467.046213859911</v>
       </c>
       <c r="E60">
-        <v>648.9399999999998</v>
+        <v>676.7699999999998</v>
       </c>
       <c r="F60">
-        <v>1614.14</v>
+        <v>1641.97</v>
       </c>
       <c r="G60">
         <v>515</v>
@@ -6207,28 +6207,28 @@
         <v>394.4</v>
       </c>
       <c r="M60">
-        <v>93.297292</v>
+        <v>94.90586599999999</v>
       </c>
       <c r="N60">
-        <v>301.102708</v>
+        <v>299.494134</v>
       </c>
       <c r="O60">
-        <v>75.275677</v>
+        <v>74.87353349999999</v>
       </c>
       <c r="P60">
-        <v>225.827031</v>
+        <v>224.6206005</v>
       </c>
       <c r="Q60">
-        <v>378.9270310000001</v>
+        <v>377.7206005</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1483148821451028</v>
+        <v>0.1505081830040053</v>
       </c>
       <c r="T60">
-        <v>1.998205863857848</v>
+        <v>2.0409573799866</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.22734670584008</v>
+        <v>4.155696761673298</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08728485503164217</v>
+        <v>0.08713445956234117</v>
       </c>
       <c r="C61">
-        <v>1340.076213859912</v>
+        <v>1321.222563788017</v>
       </c>
       <c r="D61">
-        <v>2467.046213859911</v>
+        <v>2476.022563788017</v>
       </c>
       <c r="E61">
-        <v>676.7699999999998</v>
+        <v>704.5999999999999</v>
       </c>
       <c r="F61">
-        <v>1641.97</v>
+        <v>1669.8</v>
       </c>
       <c r="G61">
         <v>515</v>
@@ -6289,28 +6289,28 @@
         <v>394.4</v>
       </c>
       <c r="M61">
-        <v>94.90586599999999</v>
+        <v>96.51444000000001</v>
       </c>
       <c r="N61">
-        <v>299.494134</v>
+        <v>297.8855599999999</v>
       </c>
       <c r="O61">
-        <v>74.87353349999999</v>
+        <v>74.47138999999999</v>
       </c>
       <c r="P61">
-        <v>224.6206005</v>
+        <v>223.41417</v>
       </c>
       <c r="Q61">
-        <v>377.7206005</v>
+        <v>376.51417</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1505081830040053</v>
+        <v>0.1528111489058529</v>
       </c>
       <c r="T61">
-        <v>2.0409573799866</v>
+        <v>2.085846471921789</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.155696761673298</v>
+        <v>4.086435148978742</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08713445956234117</v>
+        <v>0.08698406409304017</v>
       </c>
       <c r="C62">
-        <v>1321.222563788017</v>
+        <v>1302.434473169265</v>
       </c>
       <c r="D62">
-        <v>2476.022563788017</v>
+        <v>2485.064473169265</v>
       </c>
       <c r="E62">
-        <v>704.5999999999999</v>
+        <v>732.4299999999998</v>
       </c>
       <c r="F62">
-        <v>1669.8</v>
+        <v>1697.63</v>
       </c>
       <c r="G62">
         <v>515</v>
@@ -6371,28 +6371,28 @@
         <v>394.4</v>
       </c>
       <c r="M62">
-        <v>96.51444000000001</v>
+        <v>98.123014</v>
       </c>
       <c r="N62">
-        <v>297.8855599999999</v>
+        <v>296.276986</v>
       </c>
       <c r="O62">
-        <v>74.47138999999999</v>
+        <v>74.06924649999999</v>
       </c>
       <c r="P62">
-        <v>223.41417</v>
+        <v>222.2077395</v>
       </c>
       <c r="Q62">
-        <v>376.51417</v>
+        <v>375.3077395</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1528111489058529</v>
+        <v>0.1552322156231799</v>
       </c>
       <c r="T62">
-        <v>2.085846471921789</v>
+        <v>2.133037568571603</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.086435148978742</v>
+        <v>4.019444408831551</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08698406409304017</v>
+        <v>0.08846116862373918</v>
       </c>
       <c r="C63">
-        <v>1302.434473169265</v>
+        <v>1188.561354548392</v>
       </c>
       <c r="D63">
-        <v>2485.064473169265</v>
+        <v>2399.021354548392</v>
       </c>
       <c r="E63">
-        <v>732.4299999999998</v>
+        <v>760.26</v>
       </c>
       <c r="F63">
-        <v>1697.63</v>
+        <v>1725.46</v>
       </c>
       <c r="G63">
         <v>515</v>
@@ -6453,45 +6453,45 @@
         <v>394.4</v>
       </c>
       <c r="M63">
-        <v>98.123014</v>
+        <v>105.770698</v>
       </c>
       <c r="N63">
-        <v>296.276986</v>
+        <v>288.629302</v>
       </c>
       <c r="O63">
-        <v>74.06924649999999</v>
+        <v>72.1573255</v>
       </c>
       <c r="P63">
-        <v>222.2077395</v>
+        <v>216.4719765</v>
       </c>
       <c r="Q63">
-        <v>375.3077395</v>
+        <v>369.5719765</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1552322156231799</v>
+        <v>0.1577807069045768</v>
       </c>
       <c r="T63">
-        <v>2.133037568571603</v>
+        <v>2.182712407150355</v>
       </c>
       <c r="U63">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.019444408831551</v>
+        <v>3.7288210010678</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08846116862373918</v>
+        <v>0.08833702315443817</v>
       </c>
       <c r="C64">
-        <v>1188.561354548392</v>
+        <v>1167.732964201287</v>
       </c>
       <c r="D64">
-        <v>2399.021354548392</v>
+        <v>2406.022964201287</v>
       </c>
       <c r="E64">
-        <v>760.26</v>
+        <v>788.0899999999999</v>
       </c>
       <c r="F64">
-        <v>1725.46</v>
+        <v>1753.29</v>
       </c>
       <c r="G64">
         <v>515</v>
@@ -6535,28 +6535,28 @@
         <v>394.4</v>
       </c>
       <c r="M64">
-        <v>105.770698</v>
+        <v>107.476677</v>
       </c>
       <c r="N64">
-        <v>288.629302</v>
+        <v>286.923323</v>
       </c>
       <c r="O64">
-        <v>72.1573255</v>
+        <v>71.73083075</v>
       </c>
       <c r="P64">
-        <v>216.4719765</v>
+        <v>215.19249225</v>
       </c>
       <c r="Q64">
-        <v>369.5719765</v>
+        <v>368.29249225</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1577807069045768</v>
+        <v>0.1604669544714545</v>
       </c>
       <c r="T64">
-        <v>2.182712407150355</v>
+        <v>2.235072372138769</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.7288210010678</v>
+        <v>3.669633366130216</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08833702315443817</v>
+        <v>0.08821287768513715</v>
       </c>
       <c r="C65">
-        <v>1167.732964201287</v>
+        <v>1146.945562259765</v>
       </c>
       <c r="D65">
-        <v>2406.022964201287</v>
+        <v>2413.065562259765</v>
       </c>
       <c r="E65">
-        <v>788.0899999999999</v>
+        <v>815.9200000000001</v>
       </c>
       <c r="F65">
-        <v>1753.29</v>
+        <v>1781.12</v>
       </c>
       <c r="G65">
         <v>515</v>
@@ -6617,28 +6617,28 @@
         <v>394.4</v>
       </c>
       <c r="M65">
-        <v>107.476677</v>
+        <v>109.182656</v>
       </c>
       <c r="N65">
-        <v>286.923323</v>
+        <v>285.217344</v>
       </c>
       <c r="O65">
-        <v>71.73083075</v>
+        <v>71.30433599999999</v>
       </c>
       <c r="P65">
-        <v>215.19249225</v>
+        <v>213.913008</v>
       </c>
       <c r="Q65">
-        <v>368.29249225</v>
+        <v>367.013008</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1604669544714545</v>
+        <v>0.1633024380142699</v>
       </c>
       <c r="T65">
-        <v>2.235072372138769</v>
+        <v>2.290341224070984</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.669633366130216</v>
+        <v>3.612295344784431</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08821287768513715</v>
+        <v>0.08808873221583614</v>
       </c>
       <c r="C66">
-        <v>1146.945562259765</v>
+        <v>1126.199509708268</v>
       </c>
       <c r="D66">
-        <v>2413.065562259765</v>
+        <v>2420.149509708268</v>
       </c>
       <c r="E66">
-        <v>815.9200000000001</v>
+        <v>843.75</v>
       </c>
       <c r="F66">
-        <v>1781.12</v>
+        <v>1808.95</v>
       </c>
       <c r="G66">
         <v>515</v>
@@ -6699,28 +6699,28 @@
         <v>394.4</v>
       </c>
       <c r="M66">
-        <v>109.182656</v>
+        <v>110.888635</v>
       </c>
       <c r="N66">
-        <v>285.217344</v>
+        <v>283.511365</v>
       </c>
       <c r="O66">
-        <v>71.30433599999999</v>
+        <v>70.87784124999999</v>
       </c>
       <c r="P66">
-        <v>213.913008</v>
+        <v>212.63352375</v>
       </c>
       <c r="Q66">
-        <v>367.013008</v>
+        <v>365.73352375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1633024380142699</v>
+        <v>0.1662999491881033</v>
       </c>
       <c r="T66">
-        <v>2.290341224070984</v>
+        <v>2.348768296113611</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.612295344784431</v>
+        <v>3.556721570249286</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08808873221583614</v>
+        <v>0.08796458674653515</v>
       </c>
       <c r="C67">
-        <v>1126.199509708268</v>
+        <v>1105.495171782639</v>
       </c>
       <c r="D67">
-        <v>2420.149509708268</v>
+        <v>2427.275171782639</v>
       </c>
       <c r="E67">
-        <v>843.75</v>
+        <v>871.5800000000002</v>
       </c>
       <c r="F67">
-        <v>1808.95</v>
+        <v>1836.78</v>
       </c>
       <c r="G67">
         <v>515</v>
@@ -6781,28 +6781,28 @@
         <v>394.4</v>
       </c>
       <c r="M67">
-        <v>110.888635</v>
+        <v>112.594614</v>
       </c>
       <c r="N67">
-        <v>283.511365</v>
+        <v>281.805386</v>
       </c>
       <c r="O67">
-        <v>70.87784124999999</v>
+        <v>70.4513465</v>
       </c>
       <c r="P67">
-        <v>212.63352375</v>
+        <v>211.3540395</v>
       </c>
       <c r="Q67">
-        <v>365.73352375</v>
+        <v>364.4540395</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1662999491881033</v>
+        <v>0.1694737845486328</v>
       </c>
       <c r="T67">
-        <v>2.348768296113611</v>
+        <v>2.410632254746981</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.556721570249286</v>
+        <v>3.502831849487934</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08796458674653515</v>
+        <v>0.08924744127723415</v>
       </c>
       <c r="C68">
-        <v>1105.495171782639</v>
+        <v>1005.996027183181</v>
       </c>
       <c r="D68">
-        <v>2427.275171782639</v>
+        <v>2355.606027183182</v>
       </c>
       <c r="E68">
-        <v>871.5800000000002</v>
+        <v>899.4100000000001</v>
       </c>
       <c r="F68">
-        <v>1836.78</v>
+        <v>1864.61</v>
       </c>
       <c r="G68">
         <v>515</v>
@@ -6863,45 +6863,45 @@
         <v>394.4</v>
       </c>
       <c r="M68">
-        <v>112.594614</v>
+        <v>119.521501</v>
       </c>
       <c r="N68">
-        <v>281.805386</v>
+        <v>274.878499</v>
       </c>
       <c r="O68">
-        <v>70.4513465</v>
+        <v>68.71962474999999</v>
       </c>
       <c r="P68">
-        <v>211.3540395</v>
+        <v>206.15887425</v>
       </c>
       <c r="Q68">
-        <v>364.4540395</v>
+        <v>359.25887425</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1694737845486328</v>
+        <v>0.1728399735673762</v>
       </c>
       <c r="T68">
-        <v>2.410632254746981</v>
+        <v>2.476245544206616</v>
       </c>
       <c r="U68">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.502831849487934</v>
+        <v>3.29982469011998</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08924744127723415</v>
+        <v>0.08914429580793314</v>
       </c>
       <c r="C69">
-        <v>1005.996027183181</v>
+        <v>983.7716111391132</v>
       </c>
       <c r="D69">
-        <v>2355.606027183182</v>
+        <v>2361.211611139113</v>
       </c>
       <c r="E69">
-        <v>899.4100000000001</v>
+        <v>927.24</v>
       </c>
       <c r="F69">
-        <v>1864.61</v>
+        <v>1892.44</v>
       </c>
       <c r="G69">
         <v>515</v>
@@ -6945,28 +6945,28 @@
         <v>394.4</v>
       </c>
       <c r="M69">
-        <v>119.521501</v>
+        <v>121.305404</v>
       </c>
       <c r="N69">
-        <v>274.878499</v>
+        <v>273.094596</v>
       </c>
       <c r="O69">
-        <v>68.71962474999999</v>
+        <v>68.27364899999999</v>
       </c>
       <c r="P69">
-        <v>206.15887425</v>
+        <v>204.820947</v>
       </c>
       <c r="Q69">
-        <v>359.25887425</v>
+        <v>357.920947</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1728399735673762</v>
+        <v>0.1764165493997911</v>
       </c>
       <c r="T69">
-        <v>2.476245544206616</v>
+        <v>2.545959664257478</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.29982469011998</v>
+        <v>3.251297856441746</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08914429580793314</v>
+        <v>0.08904115033863214</v>
       </c>
       <c r="C70">
-        <v>983.7716111391132</v>
+        <v>961.5739377040311</v>
       </c>
       <c r="D70">
-        <v>2361.211611139113</v>
+        <v>2366.843937704031</v>
       </c>
       <c r="E70">
-        <v>927.24</v>
+        <v>955.0700000000002</v>
       </c>
       <c r="F70">
-        <v>1892.44</v>
+        <v>1920.27</v>
       </c>
       <c r="G70">
         <v>515</v>
@@ -7027,28 +7027,28 @@
         <v>394.4</v>
       </c>
       <c r="M70">
-        <v>121.305404</v>
+        <v>123.089307</v>
       </c>
       <c r="N70">
-        <v>273.094596</v>
+        <v>271.310693</v>
       </c>
       <c r="O70">
-        <v>68.27364899999999</v>
+        <v>67.82767324999999</v>
       </c>
       <c r="P70">
-        <v>204.820947</v>
+        <v>203.48301975</v>
       </c>
       <c r="Q70">
-        <v>357.920947</v>
+        <v>356.58301975</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1764165493997911</v>
+        <v>0.1802238720601037</v>
       </c>
       <c r="T70">
-        <v>2.545959664257478</v>
+        <v>2.620171469472912</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.251297856441746</v>
+        <v>3.204177597652734</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08904115033863214</v>
+        <v>0.08893800486933115</v>
       </c>
       <c r="C71">
-        <v>961.5739377040311</v>
+        <v>939.4031987073201</v>
       </c>
       <c r="D71">
-        <v>2366.843937704031</v>
+        <v>2372.50319870732</v>
       </c>
       <c r="E71">
-        <v>955.0700000000002</v>
+        <v>982.9000000000001</v>
       </c>
       <c r="F71">
-        <v>1920.27</v>
+        <v>1948.1</v>
       </c>
       <c r="G71">
         <v>515</v>
@@ -7109,28 +7109,28 @@
         <v>394.4</v>
       </c>
       <c r="M71">
-        <v>123.089307</v>
+        <v>124.87321</v>
       </c>
       <c r="N71">
-        <v>271.310693</v>
+        <v>269.5267899999999</v>
       </c>
       <c r="O71">
-        <v>67.82767324999999</v>
+        <v>67.38169749999999</v>
       </c>
       <c r="P71">
-        <v>203.48301975</v>
+        <v>202.1450925</v>
       </c>
       <c r="Q71">
-        <v>356.58301975</v>
+        <v>355.2450925</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1802238720601037</v>
+        <v>0.1842850162311038</v>
       </c>
       <c r="T71">
-        <v>2.620171469472912</v>
+        <v>2.699330728369374</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.204177597652734</v>
+        <v>3.158403631971981</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08893800486933115</v>
+        <v>0.08883485940003014</v>
       </c>
       <c r="C72">
-        <v>939.4031987073201</v>
+        <v>917.2595878174616</v>
       </c>
       <c r="D72">
-        <v>2372.50319870732</v>
+        <v>2378.189587817462</v>
       </c>
       <c r="E72">
-        <v>982.9000000000001</v>
+        <v>1010.73</v>
       </c>
       <c r="F72">
-        <v>1948.1</v>
+        <v>1975.93</v>
       </c>
       <c r="G72">
         <v>515</v>
@@ -7191,28 +7191,28 @@
         <v>394.4</v>
       </c>
       <c r="M72">
-        <v>124.87321</v>
+        <v>126.657113</v>
       </c>
       <c r="N72">
-        <v>269.5267899999999</v>
+        <v>267.7428869999999</v>
       </c>
       <c r="O72">
-        <v>67.38169749999999</v>
+        <v>66.93572174999998</v>
       </c>
       <c r="P72">
-        <v>202.1450925</v>
+        <v>200.80716525</v>
       </c>
       <c r="Q72">
-        <v>355.2450925</v>
+        <v>353.90716525</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1842850162311038</v>
+        <v>0.1886262393104488</v>
       </c>
       <c r="T72">
-        <v>2.699330728369374</v>
+        <v>2.783949246500076</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.158403631971981</v>
+        <v>3.113919073775192</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08883485940003014</v>
+        <v>0.08873171393072912</v>
       </c>
       <c r="C73">
-        <v>917.259587817462</v>
+        <v>895.1433005641277</v>
       </c>
       <c r="D73">
-        <v>2378.189587817462</v>
+        <v>2383.903300564128</v>
       </c>
       <c r="E73">
-        <v>1010.73</v>
+        <v>1038.56</v>
       </c>
       <c r="F73">
-        <v>1975.93</v>
+        <v>2003.76</v>
       </c>
       <c r="G73">
         <v>515</v>
@@ -7273,28 +7273,28 @@
         <v>394.4</v>
       </c>
       <c r="M73">
-        <v>126.657113</v>
+        <v>128.441016</v>
       </c>
       <c r="N73">
-        <v>267.742887</v>
+        <v>265.958984</v>
       </c>
       <c r="O73">
-        <v>66.93572175</v>
+        <v>66.489746</v>
       </c>
       <c r="P73">
-        <v>200.80716525</v>
+        <v>199.469238</v>
       </c>
       <c r="Q73">
-        <v>353.90716525</v>
+        <v>352.569238</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1886262393104487</v>
+        <v>0.193277549752604</v>
       </c>
       <c r="T73">
-        <v>2.783949246500075</v>
+        <v>2.874611944497255</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.113919073775193</v>
+        <v>3.070670197750538</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08873171393072912</v>
+        <v>0.08862856846142814</v>
       </c>
       <c r="C74">
-        <v>895.1433005641277</v>
+        <v>873.0545343605907</v>
       </c>
       <c r="D74">
-        <v>2383.903300564128</v>
+        <v>2389.644534360591</v>
       </c>
       <c r="E74">
-        <v>1038.56</v>
+        <v>1066.39</v>
       </c>
       <c r="F74">
-        <v>2003.76</v>
+        <v>2031.59</v>
       </c>
       <c r="G74">
         <v>515</v>
@@ -7355,28 +7355,28 @@
         <v>394.4</v>
       </c>
       <c r="M74">
-        <v>128.441016</v>
+        <v>130.224919</v>
       </c>
       <c r="N74">
-        <v>265.958984</v>
+        <v>264.175081</v>
       </c>
       <c r="O74">
-        <v>66.489746</v>
+        <v>66.04377024999999</v>
       </c>
       <c r="P74">
-        <v>199.469238</v>
+        <v>198.13131075</v>
       </c>
       <c r="Q74">
-        <v>352.569238</v>
+        <v>351.23131075</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.193277549752604</v>
+        <v>0.198273401708993</v>
       </c>
       <c r="T74">
-        <v>2.874611944497255</v>
+        <v>2.971990397901634</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.070670197750538</v>
+        <v>3.028606222438886</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08862856846142814</v>
+        <v>0.09285442299212712</v>
       </c>
       <c r="C75">
-        <v>873.0545343605907</v>
+        <v>630.615799620025</v>
       </c>
       <c r="D75">
-        <v>2389.644534360591</v>
+        <v>2175.035799620025</v>
       </c>
       <c r="E75">
-        <v>1066.39</v>
+        <v>1094.22</v>
       </c>
       <c r="F75">
-        <v>2031.59</v>
+        <v>2059.42</v>
       </c>
       <c r="G75">
         <v>515</v>
@@ -7437,45 +7437,45 @@
         <v>394.4</v>
       </c>
       <c r="M75">
-        <v>130.224919</v>
+        <v>148.072298</v>
       </c>
       <c r="N75">
-        <v>264.175081</v>
+        <v>246.327702</v>
       </c>
       <c r="O75">
-        <v>66.04377024999999</v>
+        <v>61.58192549999999</v>
       </c>
       <c r="P75">
-        <v>198.13131075</v>
+        <v>184.7457765</v>
       </c>
       <c r="Q75">
-        <v>351.23131075</v>
+        <v>337.8457765</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.198273401708993</v>
+        <v>0.2036535499697197</v>
       </c>
       <c r="T75">
-        <v>2.971990397901634</v>
+        <v>3.076859501567887</v>
       </c>
       <c r="U75">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.028606222438886</v>
+        <v>2.66356371399058</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09285442299212712</v>
+        <v>0.09280977752282613</v>
       </c>
       <c r="C76">
-        <v>630.615799620025</v>
+        <v>604.8514442398778</v>
       </c>
       <c r="D76">
-        <v>2175.035799620025</v>
+        <v>2177.101444239878</v>
       </c>
       <c r="E76">
-        <v>1094.22</v>
+        <v>1122.05</v>
       </c>
       <c r="F76">
-        <v>2059.42</v>
+        <v>2087.25</v>
       </c>
       <c r="G76">
         <v>515</v>
@@ -7519,28 +7519,28 @@
         <v>394.4</v>
       </c>
       <c r="M76">
-        <v>148.072298</v>
+        <v>150.073275</v>
       </c>
       <c r="N76">
-        <v>246.327702</v>
+        <v>244.326725</v>
       </c>
       <c r="O76">
-        <v>61.58192549999999</v>
+        <v>61.08168124999999</v>
       </c>
       <c r="P76">
-        <v>184.7457765</v>
+        <v>183.24504375</v>
       </c>
       <c r="Q76">
-        <v>337.8457765</v>
+        <v>336.34504375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2036535499697197</v>
+        <v>0.2094641100913045</v>
       </c>
       <c r="T76">
-        <v>3.076859501567887</v>
+        <v>3.190118133527442</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.66356371399058</v>
+        <v>2.628049531137372</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09280977752282613</v>
+        <v>0.0927651320535251</v>
       </c>
       <c r="C77">
-        <v>604.8514442398778</v>
+        <v>579.0910160997687</v>
       </c>
       <c r="D77">
-        <v>2177.101444239878</v>
+        <v>2179.171016099769</v>
       </c>
       <c r="E77">
-        <v>1122.05</v>
+        <v>1149.88</v>
       </c>
       <c r="F77">
-        <v>2087.25</v>
+        <v>2115.08</v>
       </c>
       <c r="G77">
         <v>515</v>
@@ -7601,28 +7601,28 @@
         <v>394.4</v>
       </c>
       <c r="M77">
-        <v>150.073275</v>
+        <v>152.074252</v>
       </c>
       <c r="N77">
-        <v>244.326725</v>
+        <v>242.325748</v>
       </c>
       <c r="O77">
-        <v>61.08168124999999</v>
+        <v>60.58143699999999</v>
       </c>
       <c r="P77">
-        <v>183.24504375</v>
+        <v>181.744311</v>
       </c>
       <c r="Q77">
-        <v>336.34504375</v>
+        <v>334.844311</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2094641100913045</v>
+        <v>0.2157588835563546</v>
       </c>
       <c r="T77">
-        <v>3.190118133527442</v>
+        <v>3.312814984816959</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.628049531137372</v>
+        <v>2.59346993204346</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0927651320535251</v>
+        <v>0.09272048658422412</v>
       </c>
       <c r="C78">
-        <v>579.0910160997687</v>
+        <v>553.3345264101581</v>
       </c>
       <c r="D78">
-        <v>2179.171016099769</v>
+        <v>2181.244526410158</v>
       </c>
       <c r="E78">
-        <v>1149.88</v>
+        <v>1177.71</v>
       </c>
       <c r="F78">
-        <v>2115.08</v>
+        <v>2142.91</v>
       </c>
       <c r="G78">
         <v>515</v>
@@ -7683,28 +7683,28 @@
         <v>394.4</v>
       </c>
       <c r="M78">
-        <v>152.074252</v>
+        <v>154.075229</v>
       </c>
       <c r="N78">
-        <v>242.325748</v>
+        <v>240.324771</v>
       </c>
       <c r="O78">
-        <v>60.58143699999999</v>
+        <v>60.08119274999999</v>
       </c>
       <c r="P78">
-        <v>181.744311</v>
+        <v>180.24357825</v>
       </c>
       <c r="Q78">
-        <v>334.844311</v>
+        <v>333.34357825</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2157588835563546</v>
+        <v>0.2226010286270614</v>
       </c>
       <c r="T78">
-        <v>3.312814984816959</v>
+        <v>3.446181127522956</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.59346993204346</v>
+        <v>2.559788504354584</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09272048658422412</v>
+        <v>0.09267584111492311</v>
       </c>
       <c r="C79">
-        <v>553.3345264101581</v>
+        <v>527.5819864242208</v>
       </c>
       <c r="D79">
-        <v>2181.244526410158</v>
+        <v>2183.321986424221</v>
       </c>
       <c r="E79">
-        <v>1177.71</v>
+        <v>1205.54</v>
       </c>
       <c r="F79">
-        <v>2142.91</v>
+        <v>2170.74</v>
       </c>
       <c r="G79">
         <v>515</v>
@@ -7765,28 +7765,28 @@
         <v>394.4</v>
       </c>
       <c r="M79">
-        <v>154.075229</v>
+        <v>156.076206</v>
       </c>
       <c r="N79">
-        <v>240.324771</v>
+        <v>238.3237939999999</v>
       </c>
       <c r="O79">
-        <v>60.08119274999999</v>
+        <v>59.58094849999998</v>
       </c>
       <c r="P79">
-        <v>180.24357825</v>
+        <v>178.7428455</v>
       </c>
       <c r="Q79">
-        <v>333.34357825</v>
+        <v>331.8428455</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2226010286270614</v>
+        <v>0.2300651868860141</v>
       </c>
       <c r="T79">
-        <v>3.446181127522956</v>
+        <v>3.591671465020406</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.559788504354584</v>
+        <v>2.526970703016704</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09267584111492311</v>
+        <v>0.09494194564562211</v>
       </c>
       <c r="C80">
-        <v>527.5819864242208</v>
+        <v>399.0714826222425</v>
       </c>
       <c r="D80">
-        <v>2183.321986424221</v>
+        <v>2082.641482622243</v>
       </c>
       <c r="E80">
-        <v>1205.54</v>
+        <v>1233.37</v>
       </c>
       <c r="F80">
-        <v>2170.74</v>
+        <v>2198.57</v>
       </c>
       <c r="G80">
         <v>515</v>
@@ -7847,45 +7847,45 @@
         <v>394.4</v>
       </c>
       <c r="M80">
-        <v>156.076206</v>
+        <v>166.651606</v>
       </c>
       <c r="N80">
-        <v>238.3237939999999</v>
+        <v>227.748394</v>
       </c>
       <c r="O80">
-        <v>59.58094849999998</v>
+        <v>56.93709849999999</v>
       </c>
       <c r="P80">
-        <v>178.7428455</v>
+        <v>170.8112955</v>
       </c>
       <c r="Q80">
-        <v>331.8428455</v>
+        <v>323.9112955</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2300651868860141</v>
+        <v>0.2382402173601053</v>
       </c>
       <c r="T80">
-        <v>3.591671465020406</v>
+        <v>3.751018025136663</v>
       </c>
       <c r="U80">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.526970703016704</v>
+        <v>2.366613856694546</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09494194564562211</v>
+        <v>0.0949265501763211</v>
       </c>
       <c r="C81">
-        <v>399.0714826222425</v>
+        <v>371.8941489074928</v>
       </c>
       <c r="D81">
-        <v>2082.641482622243</v>
+        <v>2083.294148907493</v>
       </c>
       <c r="E81">
-        <v>1233.37</v>
+        <v>1261.2</v>
       </c>
       <c r="F81">
-        <v>2198.57</v>
+        <v>2226.4</v>
       </c>
       <c r="G81">
         <v>515</v>
@@ -7929,28 +7929,28 @@
         <v>394.4</v>
       </c>
       <c r="M81">
-        <v>166.651606</v>
+        <v>168.76112</v>
       </c>
       <c r="N81">
-        <v>227.748394</v>
+        <v>225.6388799999999</v>
       </c>
       <c r="O81">
-        <v>56.93709849999999</v>
+        <v>56.40971999999999</v>
       </c>
       <c r="P81">
-        <v>170.8112955</v>
+        <v>169.22916</v>
       </c>
       <c r="Q81">
-        <v>323.9112955</v>
+        <v>322.32916</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2382402173601053</v>
+        <v>0.2472327508816055</v>
       </c>
       <c r="T81">
-        <v>3.751018025136663</v>
+        <v>3.926299241264545</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.366613856694546</v>
+        <v>2.337031183485864</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0949265501763211</v>
+        <v>0.09491115470702011</v>
       </c>
       <c r="C82">
-        <v>371.8941489074928</v>
+        <v>344.7172243911741</v>
       </c>
       <c r="D82">
-        <v>2083.294148907493</v>
+        <v>2083.947224391174</v>
       </c>
       <c r="E82">
-        <v>1261.2</v>
+        <v>1289.03</v>
       </c>
       <c r="F82">
-        <v>2226.4</v>
+        <v>2254.23</v>
       </c>
       <c r="G82">
         <v>515</v>
@@ -8011,28 +8011,28 @@
         <v>394.4</v>
       </c>
       <c r="M82">
-        <v>168.76112</v>
+        <v>170.870634</v>
       </c>
       <c r="N82">
-        <v>225.6388799999999</v>
+        <v>223.529366</v>
       </c>
       <c r="O82">
-        <v>56.40971999999999</v>
+        <v>55.88234149999999</v>
       </c>
       <c r="P82">
-        <v>169.22916</v>
+        <v>167.6470245</v>
       </c>
       <c r="Q82">
-        <v>322.32916</v>
+        <v>320.7470245</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2472327508816055</v>
+        <v>0.2571718668790532</v>
       </c>
       <c r="T82">
-        <v>3.926299241264545</v>
+        <v>4.120031111721677</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.337031183485864</v>
+        <v>2.308178946652705</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09491115470702011</v>
+        <v>0.09489575923771909</v>
       </c>
       <c r="C83">
-        <v>344.7172243911741</v>
+        <v>317.5407094582383</v>
       </c>
       <c r="D83">
-        <v>2083.947224391174</v>
+        <v>2084.600709458239</v>
       </c>
       <c r="E83">
-        <v>1289.03</v>
+        <v>1316.86</v>
       </c>
       <c r="F83">
-        <v>2254.23</v>
+        <v>2282.06</v>
       </c>
       <c r="G83">
         <v>515</v>
@@ -8093,28 +8093,28 @@
         <v>394.4</v>
       </c>
       <c r="M83">
-        <v>170.870634</v>
+        <v>172.980148</v>
       </c>
       <c r="N83">
-        <v>223.529366</v>
+        <v>221.4198519999999</v>
       </c>
       <c r="O83">
-        <v>55.88234149999999</v>
+        <v>55.35496299999998</v>
       </c>
       <c r="P83">
-        <v>167.6470245</v>
+        <v>166.0648889999999</v>
       </c>
       <c r="Q83">
-        <v>320.7470245</v>
+        <v>319.164889</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2571718668790532</v>
+        <v>0.2682153290984395</v>
       </c>
       <c r="T83">
-        <v>4.120031111721677</v>
+        <v>4.335288745562935</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.308178946652705</v>
+        <v>2.280030422913038</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09489575923771909</v>
+        <v>0.09488036376841809</v>
       </c>
       <c r="C84">
-        <v>317.5407094582383</v>
+        <v>290.3646044941179</v>
       </c>
       <c r="D84">
-        <v>2084.600709458239</v>
+        <v>2085.254604494118</v>
       </c>
       <c r="E84">
-        <v>1316.86</v>
+        <v>1344.69</v>
       </c>
       <c r="F84">
-        <v>2282.06</v>
+        <v>2309.89</v>
       </c>
       <c r="G84">
         <v>515</v>
@@ -8175,28 +8175,28 @@
         <v>394.4</v>
       </c>
       <c r="M84">
-        <v>172.980148</v>
+        <v>175.089662</v>
       </c>
       <c r="N84">
-        <v>221.4198519999999</v>
+        <v>219.3103379999999</v>
       </c>
       <c r="O84">
-        <v>55.35496299999998</v>
+        <v>54.82758449999999</v>
       </c>
       <c r="P84">
-        <v>166.0648889999999</v>
+        <v>164.4827534999999</v>
       </c>
       <c r="Q84">
-        <v>319.164889</v>
+        <v>317.5827535</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2682153290984395</v>
+        <v>0.2805580221671653</v>
       </c>
       <c r="T84">
-        <v>4.335288745562935</v>
+        <v>4.57587080691493</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.280030422913038</v>
+        <v>2.252560176853845</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09488036376841809</v>
+        <v>0.09486496829911709</v>
       </c>
       <c r="C85">
-        <v>290.3646044941179</v>
+        <v>263.1889098847282</v>
       </c>
       <c r="D85">
-        <v>2085.254604494118</v>
+        <v>2085.908909884728</v>
       </c>
       <c r="E85">
-        <v>1344.69</v>
+        <v>1372.52</v>
       </c>
       <c r="F85">
-        <v>2309.89</v>
+        <v>2337.72</v>
       </c>
       <c r="G85">
         <v>515</v>
@@ -8257,28 +8257,28 @@
         <v>394.4</v>
       </c>
       <c r="M85">
-        <v>175.089662</v>
+        <v>177.199176</v>
       </c>
       <c r="N85">
-        <v>219.3103379999999</v>
+        <v>217.200824</v>
       </c>
       <c r="O85">
-        <v>54.82758449999999</v>
+        <v>54.30020599999999</v>
       </c>
       <c r="P85">
-        <v>164.4827534999999</v>
+        <v>162.900618</v>
       </c>
       <c r="Q85">
-        <v>317.5827535</v>
+        <v>316.000618</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2805580221671653</v>
+        <v>0.2944435518694819</v>
       </c>
       <c r="T85">
-        <v>4.57587080691493</v>
+        <v>4.846525625935923</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.252560176853845</v>
+        <v>2.225743984272252</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09486496829911709</v>
+        <v>0.0948495728298161</v>
       </c>
       <c r="C86">
-        <v>263.1889098847287</v>
+        <v>236.0136260164722</v>
       </c>
       <c r="D86">
-        <v>2085.908909884728</v>
+        <v>2086.563626016472</v>
       </c>
       <c r="E86">
-        <v>1372.52</v>
+        <v>1400.35</v>
       </c>
       <c r="F86">
-        <v>2337.72</v>
+        <v>2365.55</v>
       </c>
       <c r="G86">
         <v>515</v>
@@ -8339,28 +8339,28 @@
         <v>394.4</v>
       </c>
       <c r="M86">
-        <v>177.199176</v>
+        <v>179.30869</v>
       </c>
       <c r="N86">
-        <v>217.200824</v>
+        <v>215.09131</v>
       </c>
       <c r="O86">
-        <v>54.300206</v>
+        <v>53.7728275</v>
       </c>
       <c r="P86">
-        <v>162.900618</v>
+        <v>161.3184825</v>
       </c>
       <c r="Q86">
-        <v>316.000618</v>
+        <v>314.4184825</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2944435518694817</v>
+        <v>0.3101804855321073</v>
       </c>
       <c r="T86">
-        <v>4.846525625935921</v>
+        <v>5.153267754159714</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.225743984272252</v>
+        <v>2.199558760927872</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0948495728298161</v>
+        <v>0.09483417736051508</v>
       </c>
       <c r="C87">
-        <v>236.0136260164722</v>
+        <v>208.8387532762354</v>
       </c>
       <c r="D87">
-        <v>2086.563626016472</v>
+        <v>2087.218753276235</v>
       </c>
       <c r="E87">
-        <v>1400.35</v>
+        <v>1428.18</v>
       </c>
       <c r="F87">
-        <v>2365.55</v>
+        <v>2393.38</v>
       </c>
       <c r="G87">
         <v>515</v>
@@ -8421,28 +8421,28 @@
         <v>394.4</v>
       </c>
       <c r="M87">
-        <v>179.30869</v>
+        <v>181.418204</v>
       </c>
       <c r="N87">
-        <v>215.09131</v>
+        <v>212.9817959999999</v>
       </c>
       <c r="O87">
-        <v>53.7728275</v>
+        <v>53.24544899999999</v>
       </c>
       <c r="P87">
-        <v>161.3184825</v>
+        <v>159.736347</v>
       </c>
       <c r="Q87">
-        <v>314.4184825</v>
+        <v>312.836347</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3101804855321073</v>
+        <v>0.3281655525751077</v>
       </c>
       <c r="T87">
-        <v>5.153267754159714</v>
+        <v>5.503830186415476</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.199558760927872</v>
+        <v>2.17398249626592</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09483417736051508</v>
+        <v>0.09481878189121407</v>
       </c>
       <c r="C88">
-        <v>208.8387532762354</v>
+        <v>181.6642920513905</v>
       </c>
       <c r="D88">
-        <v>2087.218753276235</v>
+        <v>2087.874292051391</v>
       </c>
       <c r="E88">
-        <v>1428.18</v>
+        <v>1456.01</v>
       </c>
       <c r="F88">
-        <v>2393.38</v>
+        <v>2421.21</v>
       </c>
       <c r="G88">
         <v>515</v>
@@ -8503,28 +8503,28 @@
         <v>394.4</v>
       </c>
       <c r="M88">
-        <v>181.418204</v>
+        <v>183.527718</v>
       </c>
       <c r="N88">
-        <v>212.9817959999999</v>
+        <v>210.872282</v>
       </c>
       <c r="O88">
-        <v>53.24544899999999</v>
+        <v>52.71807049999999</v>
       </c>
       <c r="P88">
-        <v>159.736347</v>
+        <v>158.1542115</v>
       </c>
       <c r="Q88">
-        <v>312.836347</v>
+        <v>311.2542115</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3281655525751077</v>
+        <v>0.348917553009339</v>
       </c>
       <c r="T88">
-        <v>5.503830186415476</v>
+        <v>5.90832530055674</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.17398249626592</v>
+        <v>2.148994191711139</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09481878189121407</v>
+        <v>0.09480338642191308</v>
       </c>
       <c r="C89">
-        <v>181.6642920513905</v>
+        <v>154.4902427297957</v>
       </c>
       <c r="D89">
-        <v>2087.874292051391</v>
+        <v>2088.530242729796</v>
       </c>
       <c r="E89">
-        <v>1456.01</v>
+        <v>1483.84</v>
       </c>
       <c r="F89">
-        <v>2421.21</v>
+        <v>2449.04</v>
       </c>
       <c r="G89">
         <v>515</v>
@@ -8585,28 +8585,28 @@
         <v>394.4</v>
       </c>
       <c r="M89">
-        <v>183.527718</v>
+        <v>185.637232</v>
       </c>
       <c r="N89">
-        <v>210.872282</v>
+        <v>208.762768</v>
       </c>
       <c r="O89">
-        <v>52.71807049999999</v>
+        <v>52.19069199999999</v>
       </c>
       <c r="P89">
-        <v>158.1542115</v>
+        <v>156.572076</v>
       </c>
       <c r="Q89">
-        <v>311.2542115</v>
+        <v>309.672076</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.348917553009339</v>
+        <v>0.3731282201826089</v>
       </c>
       <c r="T89">
-        <v>5.90832530055674</v>
+        <v>6.380236267054883</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.148994191711139</v>
+        <v>2.124573803168968</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09480338642191308</v>
+        <v>0.09478799095261206</v>
       </c>
       <c r="C90">
-        <v>154.4902427297957</v>
+        <v>127.3166056997998</v>
       </c>
       <c r="D90">
-        <v>2088.530242729796</v>
+        <v>2089.1866056998</v>
       </c>
       <c r="E90">
-        <v>1483.84</v>
+        <v>1511.67</v>
       </c>
       <c r="F90">
-        <v>2449.04</v>
+        <v>2476.87</v>
       </c>
       <c r="G90">
         <v>515</v>
@@ -8667,28 +8667,28 @@
         <v>394.4</v>
       </c>
       <c r="M90">
-        <v>185.637232</v>
+        <v>187.746746</v>
       </c>
       <c r="N90">
-        <v>208.762768</v>
+        <v>206.653254</v>
       </c>
       <c r="O90">
-        <v>52.19069199999999</v>
+        <v>51.66331349999999</v>
       </c>
       <c r="P90">
-        <v>156.572076</v>
+        <v>154.9899405</v>
       </c>
       <c r="Q90">
-        <v>309.672076</v>
+        <v>308.0899405</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3731282201826089</v>
+        <v>0.4017408268419279</v>
       </c>
       <c r="T90">
-        <v>6.380236267054883</v>
+        <v>6.937949227461779</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.124573803168968</v>
+        <v>2.100702187403024</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09478799095261206</v>
+        <v>0.09477259548331107</v>
       </c>
       <c r="C91">
-        <v>127.3166056997998</v>
+        <v>100.1433813502354</v>
       </c>
       <c r="D91">
-        <v>2089.1866056998</v>
+        <v>2089.843381350236</v>
       </c>
       <c r="E91">
-        <v>1511.67</v>
+        <v>1539.5</v>
       </c>
       <c r="F91">
-        <v>2476.87</v>
+        <v>2504.7</v>
       </c>
       <c r="G91">
         <v>515</v>
@@ -8749,28 +8749,28 @@
         <v>394.4</v>
       </c>
       <c r="M91">
-        <v>187.746746</v>
+        <v>189.85626</v>
       </c>
       <c r="N91">
-        <v>206.653254</v>
+        <v>204.5437399999999</v>
       </c>
       <c r="O91">
-        <v>51.66331349999999</v>
+        <v>51.13593499999998</v>
       </c>
       <c r="P91">
-        <v>154.9899405</v>
+        <v>153.4078049999999</v>
       </c>
       <c r="Q91">
-        <v>308.0899405</v>
+        <v>306.507805</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4017408268419279</v>
+        <v>0.4360759548331107</v>
       </c>
       <c r="T91">
-        <v>6.937949227461779</v>
+        <v>7.607204779950055</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.100702187403024</v>
+        <v>2.077361051987435</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09477259548331107</v>
+        <v>0.09475720001401006</v>
       </c>
       <c r="C92">
-        <v>100.1433813502354</v>
+        <v>72.97057007042986</v>
       </c>
       <c r="D92">
-        <v>2089.843381350236</v>
+        <v>2090.50057007043</v>
       </c>
       <c r="E92">
-        <v>1539.5</v>
+        <v>1567.33</v>
       </c>
       <c r="F92">
-        <v>2504.7</v>
+        <v>2532.53</v>
       </c>
       <c r="G92">
         <v>515</v>
@@ -8831,28 +8831,28 @@
         <v>394.4</v>
       </c>
       <c r="M92">
-        <v>189.85626</v>
+        <v>191.965774</v>
       </c>
       <c r="N92">
-        <v>204.5437399999999</v>
+        <v>202.4342259999999</v>
       </c>
       <c r="O92">
-        <v>51.13593499999998</v>
+        <v>50.60855649999998</v>
       </c>
       <c r="P92">
-        <v>153.4078049999999</v>
+        <v>151.8256694999999</v>
       </c>
       <c r="Q92">
-        <v>306.507805</v>
+        <v>304.9256695</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4360759548331107</v>
+        <v>0.4780411112667786</v>
       </c>
       <c r="T92">
-        <v>7.607204779950055</v>
+        <v>8.425183788546835</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.077361051987435</v>
+        <v>2.054532908559001</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09475720001401006</v>
+        <v>0.09474180454470907</v>
       </c>
       <c r="C93">
-        <v>72.97057007042986</v>
+        <v>45.79817225019497</v>
       </c>
       <c r="D93">
-        <v>2090.50057007043</v>
+        <v>2091.158172250195</v>
       </c>
       <c r="E93">
-        <v>1567.33</v>
+        <v>1595.16</v>
       </c>
       <c r="F93">
-        <v>2532.53</v>
+        <v>2560.36</v>
       </c>
       <c r="G93">
         <v>515</v>
@@ -8913,28 +8913,28 @@
         <v>394.4</v>
       </c>
       <c r="M93">
-        <v>191.965774</v>
+        <v>194.075288</v>
       </c>
       <c r="N93">
-        <v>202.4342259999999</v>
+        <v>200.3247119999999</v>
       </c>
       <c r="O93">
-        <v>50.60855649999998</v>
+        <v>50.08117799999999</v>
       </c>
       <c r="P93">
-        <v>151.8256694999999</v>
+        <v>150.243534</v>
       </c>
       <c r="Q93">
-        <v>304.9256695</v>
+        <v>303.343534</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4780411112667786</v>
+        <v>0.5304975568088635</v>
       </c>
       <c r="T93">
-        <v>8.425183788546835</v>
+        <v>9.447657549292813</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.054532908559001</v>
+        <v>2.032201029118143</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09474180454470907</v>
+        <v>0.09472640907540805</v>
       </c>
       <c r="C94">
-        <v>45.79817225019497</v>
+        <v>18.6261882798367</v>
       </c>
       <c r="D94">
-        <v>2091.158172250195</v>
+        <v>2091.816188279837</v>
       </c>
       <c r="E94">
-        <v>1595.16</v>
+        <v>1622.99</v>
       </c>
       <c r="F94">
-        <v>2560.36</v>
+        <v>2588.19</v>
       </c>
       <c r="G94">
         <v>515</v>
@@ -8995,28 +8995,28 @@
         <v>394.4</v>
       </c>
       <c r="M94">
-        <v>194.075288</v>
+        <v>196.184802</v>
       </c>
       <c r="N94">
-        <v>200.3247119999999</v>
+        <v>198.215198</v>
       </c>
       <c r="O94">
-        <v>50.08117799999999</v>
+        <v>49.55379949999999</v>
       </c>
       <c r="P94">
-        <v>150.243534</v>
+        <v>148.6613985</v>
       </c>
       <c r="Q94">
-        <v>303.343534</v>
+        <v>301.7613985</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5304975568088635</v>
+        <v>0.5979415582201154</v>
       </c>
       <c r="T94">
-        <v>9.447657549292813</v>
+        <v>10.76226667025193</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.032201029118143</v>
+        <v>2.01034940514913</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09472640907540805</v>
+        <v>0.104722013606107</v>
       </c>
       <c r="C95">
-        <v>18.6261882798367</v>
+        <v>-364.0621420673847</v>
       </c>
       <c r="D95">
-        <v>2091.816188279837</v>
+        <v>1736.957857932615</v>
       </c>
       <c r="E95">
-        <v>1622.99</v>
+        <v>1650.82</v>
       </c>
       <c r="F95">
-        <v>2588.19</v>
+        <v>2616.02</v>
       </c>
       <c r="G95">
         <v>515</v>
@@ -9077,45 +9077,45 @@
         <v>394.4</v>
       </c>
       <c r="M95">
-        <v>196.184802</v>
+        <v>235.4418</v>
       </c>
       <c r="N95">
-        <v>198.215198</v>
+        <v>158.9582</v>
       </c>
       <c r="O95">
-        <v>49.55379949999999</v>
+        <v>39.73954999999999</v>
       </c>
       <c r="P95">
-        <v>148.6613985</v>
+        <v>119.21865</v>
       </c>
       <c r="Q95">
-        <v>301.7613985</v>
+        <v>272.31865</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5979415582201154</v>
+        <v>0.687866893435118</v>
       </c>
       <c r="T95">
-        <v>10.76226667025193</v>
+        <v>12.51507883153074</v>
       </c>
       <c r="U95">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V95">
         <v>0.25</v>
       </c>
       <c r="W95">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.01034940514913</v>
+        <v>1.675148592985612</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.104722013606107</v>
+        <v>0.104813118136806</v>
       </c>
       <c r="C96">
-        <v>-364.0621420673847</v>
+        <v>-394.5736599313295</v>
       </c>
       <c r="D96">
-        <v>1736.957857932615</v>
+        <v>1734.276340068671</v>
       </c>
       <c r="E96">
-        <v>1650.82</v>
+        <v>1678.65</v>
       </c>
       <c r="F96">
-        <v>2616.02</v>
+        <v>2643.85</v>
       </c>
       <c r="G96">
         <v>515</v>
@@ -9159,28 +9159,28 @@
         <v>394.4</v>
       </c>
       <c r="M96">
-        <v>235.4418</v>
+        <v>237.9465</v>
       </c>
       <c r="N96">
-        <v>158.9582</v>
+        <v>156.4535</v>
       </c>
       <c r="O96">
-        <v>39.73954999999999</v>
+        <v>39.11337499999999</v>
       </c>
       <c r="P96">
-        <v>119.21865</v>
+        <v>117.340125</v>
       </c>
       <c r="Q96">
-        <v>272.31865</v>
+        <v>270.440125</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.687866893435118</v>
+        <v>0.8137623627361219</v>
       </c>
       <c r="T96">
-        <v>12.51507883153074</v>
+        <v>14.96901585732109</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.675148592985612</v>
+        <v>1.657515449901553</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.104813118136806</v>
+        <v>0.104904222667505</v>
       </c>
       <c r="C97">
-        <v>-394.5736599313295</v>
+        <v>-425.0769110956862</v>
       </c>
       <c r="D97">
-        <v>1734.276340068671</v>
+        <v>1731.603088904314</v>
       </c>
       <c r="E97">
-        <v>1678.65</v>
+        <v>1706.48</v>
       </c>
       <c r="F97">
-        <v>2643.85</v>
+        <v>2671.68</v>
       </c>
       <c r="G97">
         <v>515</v>
@@ -9241,28 +9241,28 @@
         <v>394.4</v>
       </c>
       <c r="M97">
-        <v>237.9465</v>
+        <v>240.4512</v>
       </c>
       <c r="N97">
-        <v>156.4535</v>
+        <v>153.9487999999999</v>
       </c>
       <c r="O97">
-        <v>39.11337499999999</v>
+        <v>38.48719999999999</v>
       </c>
       <c r="P97">
-        <v>117.340125</v>
+        <v>115.4616</v>
       </c>
       <c r="Q97">
-        <v>270.440125</v>
+        <v>268.5616</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8137623627361219</v>
+        <v>1.002605566687628</v>
       </c>
       <c r="T97">
-        <v>14.96901585732109</v>
+        <v>18.64992139600662</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.657515449901553</v>
+        <v>1.640249663965079</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.104904222667505</v>
+        <v>0.104995327198204</v>
       </c>
       <c r="C98">
-        <v>-425.0769110956858</v>
+        <v>-455.5719337290325</v>
       </c>
       <c r="D98">
-        <v>1731.603088904314</v>
+        <v>1728.938066270967</v>
       </c>
       <c r="E98">
-        <v>1706.48</v>
+        <v>1734.31</v>
       </c>
       <c r="F98">
-        <v>2671.68</v>
+        <v>2699.51</v>
       </c>
       <c r="G98">
         <v>515</v>
@@ -9323,28 +9323,28 @@
         <v>394.4</v>
       </c>
       <c r="M98">
-        <v>240.4512</v>
+        <v>242.9559</v>
       </c>
       <c r="N98">
-        <v>153.9488</v>
+        <v>151.4441</v>
       </c>
       <c r="O98">
-        <v>38.4872</v>
+        <v>37.86102500000001</v>
       </c>
       <c r="P98">
-        <v>115.4616</v>
+        <v>113.583075</v>
       </c>
       <c r="Q98">
-        <v>268.5616</v>
+        <v>266.683075</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.002605566687625</v>
+        <v>1.317344239940134</v>
       </c>
       <c r="T98">
-        <v>18.64992139600657</v>
+        <v>24.78476396048241</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.640249663965079</v>
+        <v>1.623339873614924</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.104995327198204</v>
+        <v>0.105086431728903</v>
       </c>
       <c r="C99">
-        <v>-455.5719337290325</v>
+        <v>-486.0587657653323</v>
       </c>
       <c r="D99">
-        <v>1728.938066270967</v>
+        <v>1726.281234234668</v>
       </c>
       <c r="E99">
-        <v>1734.31</v>
+        <v>1762.14</v>
       </c>
       <c r="F99">
-        <v>2699.51</v>
+        <v>2727.34</v>
       </c>
       <c r="G99">
         <v>515</v>
@@ -9405,28 +9405,28 @@
         <v>394.4</v>
       </c>
       <c r="M99">
-        <v>242.9559</v>
+        <v>245.4606</v>
       </c>
       <c r="N99">
-        <v>151.4441</v>
+        <v>148.9394</v>
       </c>
       <c r="O99">
-        <v>37.86102500000001</v>
+        <v>37.23484999999999</v>
       </c>
       <c r="P99">
-        <v>113.583075</v>
+        <v>111.70455</v>
       </c>
       <c r="Q99">
-        <v>266.683075</v>
+        <v>264.80455</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.317344239940134</v>
+        <v>1.94682158644515</v>
       </c>
       <c r="T99">
-        <v>24.78476396048241</v>
+        <v>37.0544490894341</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.623339873614924</v>
+        <v>1.606775181027016</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.105086431728903</v>
+        <v>0.1051775362596021</v>
       </c>
       <c r="C100">
-        <v>-486.0587657653323</v>
+        <v>-516.5374449057376</v>
       </c>
       <c r="D100">
-        <v>1726.281234234668</v>
+        <v>1723.632555094262</v>
       </c>
       <c r="E100">
-        <v>1762.14</v>
+        <v>1789.97</v>
       </c>
       <c r="F100">
-        <v>2727.34</v>
+        <v>2755.17</v>
       </c>
       <c r="G100">
         <v>515</v>
@@ -9487,28 +9487,28 @@
         <v>394.4</v>
       </c>
       <c r="M100">
-        <v>245.4606</v>
+        <v>247.9653</v>
       </c>
       <c r="N100">
-        <v>148.9394</v>
+        <v>146.4347</v>
       </c>
       <c r="O100">
-        <v>37.23484999999999</v>
+        <v>36.608675</v>
       </c>
       <c r="P100">
-        <v>111.70455</v>
+        <v>109.826025</v>
       </c>
       <c r="Q100">
-        <v>264.80455</v>
+        <v>262.926025</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.94682158644515</v>
+        <v>3.8352536259602</v>
       </c>
       <c r="T100">
-        <v>37.0544490894341</v>
+        <v>73.86350447628917</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.606775181027016</v>
+        <v>1.59054512869341</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1051775362596021</v>
-      </c>
-      <c r="C101">
-        <v>-516.5374449057376</v>
-      </c>
-      <c r="D101">
-        <v>1723.632555094262</v>
-      </c>
-      <c r="E101">
-        <v>1789.97</v>
-      </c>
-      <c r="F101">
-        <v>2755.17</v>
-      </c>
-      <c r="G101">
-        <v>515</v>
-      </c>
-      <c r="H101">
-        <v>1817.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>547.5</v>
-      </c>
-      <c r="K101">
-        <v>153.1</v>
-      </c>
-      <c r="L101">
-        <v>394.4</v>
-      </c>
-      <c r="M101">
-        <v>247.9653</v>
-      </c>
-      <c r="N101">
-        <v>146.4347</v>
-      </c>
-      <c r="O101">
-        <v>36.608675</v>
-      </c>
-      <c r="P101">
-        <v>109.826025</v>
-      </c>
-      <c r="Q101">
-        <v>262.926025</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.8352536259602</v>
-      </c>
-      <c r="T101">
-        <v>73.86350447628917</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.0675</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.59054512869341</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
